--- a/data/diemrenluyen.xlsx
+++ b/data/diemrenluyen.xlsx
@@ -5,22 +5,35 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/nguyenthingocmai/Documents/Thạc sĩ/Hoithao/baibao2/code v6/dulieu/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/nguyenthingocmai/Documents/Thạc sĩ/modelAI/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3D1F5CF0-CF14-094D-927F-46A76E393A8F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{836E1219-0600-A84A-B86D-9A4D8E0DCBAC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="740" windowWidth="30240" windowHeight="18900" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="760" windowWidth="30240" windowHeight="18880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="144525"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8799" uniqueCount="624">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10329" uniqueCount="931">
   <si>
     <t>2021-2022</t>
   </si>
@@ -1892,13 +1905,934 @@
   </si>
   <si>
     <t>Phan Đinh Vũ Thiên An</t>
+  </si>
+  <si>
+    <t>22050001</t>
+  </si>
+  <si>
+    <t>22050008</t>
+  </si>
+  <si>
+    <t>Bùi Văn Anh Thế</t>
+  </si>
+  <si>
+    <t>22050012</t>
+  </si>
+  <si>
+    <t>22050015</t>
+  </si>
+  <si>
+    <t>22050017</t>
+  </si>
+  <si>
+    <t>22050020</t>
+  </si>
+  <si>
+    <t>22050023</t>
+  </si>
+  <si>
+    <t>22050024</t>
+  </si>
+  <si>
+    <t>22050025</t>
+  </si>
+  <si>
+    <t>22050026</t>
+  </si>
+  <si>
+    <t>22050033</t>
+  </si>
+  <si>
+    <t>22050034</t>
+  </si>
+  <si>
+    <t>22050035</t>
+  </si>
+  <si>
+    <t>22050037</t>
+  </si>
+  <si>
+    <t>22050038</t>
+  </si>
+  <si>
+    <t>22050040</t>
+  </si>
+  <si>
+    <t>22050042</t>
+  </si>
+  <si>
+    <t>22050044</t>
+  </si>
+  <si>
+    <t>22050053</t>
+  </si>
+  <si>
+    <t>22050055</t>
+  </si>
+  <si>
+    <t>22050056</t>
+  </si>
+  <si>
+    <t>22050058</t>
+  </si>
+  <si>
+    <t>22050059</t>
+  </si>
+  <si>
+    <t>22050061</t>
+  </si>
+  <si>
+    <t>22050072</t>
+  </si>
+  <si>
+    <t>22050073</t>
+  </si>
+  <si>
+    <t>22050076</t>
+  </si>
+  <si>
+    <t>22050079</t>
+  </si>
+  <si>
+    <t>22050082</t>
+  </si>
+  <si>
+    <t>22050083</t>
+  </si>
+  <si>
+    <t>22050086</t>
+  </si>
+  <si>
+    <t>22050089</t>
+  </si>
+  <si>
+    <t>22070003</t>
+  </si>
+  <si>
+    <t>22050002</t>
+  </si>
+  <si>
+    <t>22050004</t>
+  </si>
+  <si>
+    <t>22050006</t>
+  </si>
+  <si>
+    <t>22050007</t>
+  </si>
+  <si>
+    <t>22050010</t>
+  </si>
+  <si>
+    <t>22050011</t>
+  </si>
+  <si>
+    <t>22050018</t>
+  </si>
+  <si>
+    <t>22050022</t>
+  </si>
+  <si>
+    <t>22050029</t>
+  </si>
+  <si>
+    <t>22050030</t>
+  </si>
+  <si>
+    <t>22050036</t>
+  </si>
+  <si>
+    <t>22050039</t>
+  </si>
+  <si>
+    <t>22050062</t>
+  </si>
+  <si>
+    <t>22050066</t>
+  </si>
+  <si>
+    <t>22050067</t>
+  </si>
+  <si>
+    <t>22050068</t>
+  </si>
+  <si>
+    <t>22050081</t>
+  </si>
+  <si>
+    <t>22050084</t>
+  </si>
+  <si>
+    <t>22050090</t>
+  </si>
+  <si>
+    <t>22050091</t>
+  </si>
+  <si>
+    <t>22050093</t>
+  </si>
+  <si>
+    <t>22050094</t>
+  </si>
+  <si>
+    <t>22050095</t>
+  </si>
+  <si>
+    <t>22050096</t>
+  </si>
+  <si>
+    <t>22050098</t>
+  </si>
+  <si>
+    <t>22050099</t>
+  </si>
+  <si>
+    <t>22050101</t>
+  </si>
+  <si>
+    <t>22050102</t>
+  </si>
+  <si>
+    <t>22050110</t>
+  </si>
+  <si>
+    <t>22050111</t>
+  </si>
+  <si>
+    <t>22050112</t>
+  </si>
+  <si>
+    <t>22050119</t>
+  </si>
+  <si>
+    <t>23050001</t>
+  </si>
+  <si>
+    <t>23050002</t>
+  </si>
+  <si>
+    <t>23050004</t>
+  </si>
+  <si>
+    <t>23050005</t>
+  </si>
+  <si>
+    <t>23050006</t>
+  </si>
+  <si>
+    <t>23050007</t>
+  </si>
+  <si>
+    <t>23050008</t>
+  </si>
+  <si>
+    <t>23050010</t>
+  </si>
+  <si>
+    <t>23050011</t>
+  </si>
+  <si>
+    <t>23050012</t>
+  </si>
+  <si>
+    <t>23050013</t>
+  </si>
+  <si>
+    <t>23050014</t>
+  </si>
+  <si>
+    <t>23050015</t>
+  </si>
+  <si>
+    <t>23050016</t>
+  </si>
+  <si>
+    <t>23050017</t>
+  </si>
+  <si>
+    <t>23050018</t>
+  </si>
+  <si>
+    <t>23050020</t>
+  </si>
+  <si>
+    <t>23050021</t>
+  </si>
+  <si>
+    <t>23050025</t>
+  </si>
+  <si>
+    <t>23050026</t>
+  </si>
+  <si>
+    <t>23050028</t>
+  </si>
+  <si>
+    <t>23050029</t>
+  </si>
+  <si>
+    <t>23050030</t>
+  </si>
+  <si>
+    <t>23050031</t>
+  </si>
+  <si>
+    <t>23050033</t>
+  </si>
+  <si>
+    <t>23050034</t>
+  </si>
+  <si>
+    <t>23050038</t>
+  </si>
+  <si>
+    <t>23050040</t>
+  </si>
+  <si>
+    <t>23050041</t>
+  </si>
+  <si>
+    <t>23050042</t>
+  </si>
+  <si>
+    <t>23050043</t>
+  </si>
+  <si>
+    <t>23050044</t>
+  </si>
+  <si>
+    <t>23050045</t>
+  </si>
+  <si>
+    <t>23050046</t>
+  </si>
+  <si>
+    <t>23050047</t>
+  </si>
+  <si>
+    <t>23050048</t>
+  </si>
+  <si>
+    <t>23050050</t>
+  </si>
+  <si>
+    <t>23050051</t>
+  </si>
+  <si>
+    <t>23050053</t>
+  </si>
+  <si>
+    <t>23050054</t>
+  </si>
+  <si>
+    <t>23050055</t>
+  </si>
+  <si>
+    <t>23050056</t>
+  </si>
+  <si>
+    <t>23050061</t>
+  </si>
+  <si>
+    <t>23050062</t>
+  </si>
+  <si>
+    <t>23050063</t>
+  </si>
+  <si>
+    <t>23050064</t>
+  </si>
+  <si>
+    <t>23050067</t>
+  </si>
+  <si>
+    <t>23050069</t>
+  </si>
+  <si>
+    <t>23050070</t>
+  </si>
+  <si>
+    <t>23050071</t>
+  </si>
+  <si>
+    <t>23050072</t>
+  </si>
+  <si>
+    <t>23050074</t>
+  </si>
+  <si>
+    <t>23050075</t>
+  </si>
+  <si>
+    <t>23050076</t>
+  </si>
+  <si>
+    <t>23050077</t>
+  </si>
+  <si>
+    <t>23050079</t>
+  </si>
+  <si>
+    <t>23050080</t>
+  </si>
+  <si>
+    <t>23050083</t>
+  </si>
+  <si>
+    <t>23050084</t>
+  </si>
+  <si>
+    <t>23050087</t>
+  </si>
+  <si>
+    <t>23050088</t>
+  </si>
+  <si>
+    <t>23050089</t>
+  </si>
+  <si>
+    <t>23050090</t>
+  </si>
+  <si>
+    <t>23050091</t>
+  </si>
+  <si>
+    <t>23050092</t>
+  </si>
+  <si>
+    <t>23050093</t>
+  </si>
+  <si>
+    <t>23050094</t>
+  </si>
+  <si>
+    <t>23050095</t>
+  </si>
+  <si>
+    <t>23050097</t>
+  </si>
+  <si>
+    <t>23050098</t>
+  </si>
+  <si>
+    <t>23050099</t>
+  </si>
+  <si>
+    <t>23050100</t>
+  </si>
+  <si>
+    <t>23050102</t>
+  </si>
+  <si>
+    <t>23050103</t>
+  </si>
+  <si>
+    <t>23050104</t>
+  </si>
+  <si>
+    <t>23050105</t>
+  </si>
+  <si>
+    <t>23050109</t>
+  </si>
+  <si>
+    <t>23050110</t>
+  </si>
+  <si>
+    <t>23050111</t>
+  </si>
+  <si>
+    <t>23050112</t>
+  </si>
+  <si>
+    <t>23050114</t>
+  </si>
+  <si>
+    <t>23050115</t>
+  </si>
+  <si>
+    <t>23050116</t>
+  </si>
+  <si>
+    <t>23050117</t>
+  </si>
+  <si>
+    <t>23050118</t>
+  </si>
+  <si>
+    <t>23050119</t>
+  </si>
+  <si>
+    <t>23050120</t>
+  </si>
+  <si>
+    <t>23050121</t>
+  </si>
+  <si>
+    <t>23050123</t>
+  </si>
+  <si>
+    <t>23050127</t>
+  </si>
+  <si>
+    <t>23050128</t>
+  </si>
+  <si>
+    <t>23050129</t>
+  </si>
+  <si>
+    <t>23050130</t>
+  </si>
+  <si>
+    <t>23050133</t>
+  </si>
+  <si>
+    <t>23050136</t>
+  </si>
+  <si>
+    <t>23050138</t>
+  </si>
+  <si>
+    <t>23050141</t>
+  </si>
+  <si>
+    <t>23050142</t>
+  </si>
+  <si>
+    <t>23050144</t>
+  </si>
+  <si>
+    <t>23050148</t>
+  </si>
+  <si>
+    <t>23050149</t>
+  </si>
+  <si>
+    <t>23050150</t>
+  </si>
+  <si>
+    <t>23050151</t>
+  </si>
+  <si>
+    <t>23050154</t>
+  </si>
+  <si>
+    <t>23050155</t>
+  </si>
+  <si>
+    <t>23050156</t>
+  </si>
+  <si>
+    <t>23050157</t>
+  </si>
+  <si>
+    <t>23050158</t>
+  </si>
+  <si>
+    <t>23050160</t>
+  </si>
+  <si>
+    <t>23050163</t>
+  </si>
+  <si>
+    <t>23050165</t>
+  </si>
+  <si>
+    <t>23050166</t>
+  </si>
+  <si>
+    <t>23050167</t>
+  </si>
+  <si>
+    <t>23050168</t>
+  </si>
+  <si>
+    <t>23050169</t>
+  </si>
+  <si>
+    <t>23050170</t>
+  </si>
+  <si>
+    <t>23050171</t>
+  </si>
+  <si>
+    <t>23050172</t>
+  </si>
+  <si>
+    <t>23050175</t>
+  </si>
+  <si>
+    <t>23050178</t>
+  </si>
+  <si>
+    <t>23050179</t>
+  </si>
+  <si>
+    <t>23050180</t>
+  </si>
+  <si>
+    <t>23050181</t>
+  </si>
+  <si>
+    <t>23050182</t>
+  </si>
+  <si>
+    <t>23050183</t>
+  </si>
+  <si>
+    <t>23050184</t>
+  </si>
+  <si>
+    <t>23050188</t>
+  </si>
+  <si>
+    <t>23050189</t>
+  </si>
+  <si>
+    <t>24050001</t>
+  </si>
+  <si>
+    <t>24050002</t>
+  </si>
+  <si>
+    <t>24050003</t>
+  </si>
+  <si>
+    <t>24050004</t>
+  </si>
+  <si>
+    <t>24050005</t>
+  </si>
+  <si>
+    <t>24050006</t>
+  </si>
+  <si>
+    <t>24050007</t>
+  </si>
+  <si>
+    <t>24050008</t>
+  </si>
+  <si>
+    <t>24050009</t>
+  </si>
+  <si>
+    <t>24050010</t>
+  </si>
+  <si>
+    <t>24050011</t>
+  </si>
+  <si>
+    <t>24050012</t>
+  </si>
+  <si>
+    <t>24050013</t>
+  </si>
+  <si>
+    <t>24050014</t>
+  </si>
+  <si>
+    <t>24050015</t>
+  </si>
+  <si>
+    <t>24050016</t>
+  </si>
+  <si>
+    <t>24050018</t>
+  </si>
+  <si>
+    <t>24050019</t>
+  </si>
+  <si>
+    <t>24050020</t>
+  </si>
+  <si>
+    <t>24050021</t>
+  </si>
+  <si>
+    <t>24050022</t>
+  </si>
+  <si>
+    <t>24050023</t>
+  </si>
+  <si>
+    <t>24050024</t>
+  </si>
+  <si>
+    <t>24050025</t>
+  </si>
+  <si>
+    <t>24050026</t>
+  </si>
+  <si>
+    <t>24050027</t>
+  </si>
+  <si>
+    <t>24050028</t>
+  </si>
+  <si>
+    <t>24050029</t>
+  </si>
+  <si>
+    <t>24050030</t>
+  </si>
+  <si>
+    <t>24050031</t>
+  </si>
+  <si>
+    <t>24050032</t>
+  </si>
+  <si>
+    <t>24050033</t>
+  </si>
+  <si>
+    <t>24050034</t>
+  </si>
+  <si>
+    <t>24050035</t>
+  </si>
+  <si>
+    <t>24050036</t>
+  </si>
+  <si>
+    <t>24050039</t>
+  </si>
+  <si>
+    <t>24050040</t>
+  </si>
+  <si>
+    <t>24050041</t>
+  </si>
+  <si>
+    <t>24050042</t>
+  </si>
+  <si>
+    <t>24050043</t>
+  </si>
+  <si>
+    <t>24050044</t>
+  </si>
+  <si>
+    <t>24050045</t>
+  </si>
+  <si>
+    <t>24050133</t>
+  </si>
+  <si>
+    <t>24050046</t>
+  </si>
+  <si>
+    <t>24050047</t>
+  </si>
+  <si>
+    <t>24050048</t>
+  </si>
+  <si>
+    <t>24050049</t>
+  </si>
+  <si>
+    <t>24050050</t>
+  </si>
+  <si>
+    <t>24050051</t>
+  </si>
+  <si>
+    <t>24050053</t>
+  </si>
+  <si>
+    <t>24050054</t>
+  </si>
+  <si>
+    <t>24050055</t>
+  </si>
+  <si>
+    <t>24050056</t>
+  </si>
+  <si>
+    <t>24050057</t>
+  </si>
+  <si>
+    <t>24050058</t>
+  </si>
+  <si>
+    <t>24050060</t>
+  </si>
+  <si>
+    <t>24050061</t>
+  </si>
+  <si>
+    <t>24050062</t>
+  </si>
+  <si>
+    <t>24050063</t>
+  </si>
+  <si>
+    <t>24050064</t>
+  </si>
+  <si>
+    <t>24050065</t>
+  </si>
+  <si>
+    <t>24050066</t>
+  </si>
+  <si>
+    <t>24050067</t>
+  </si>
+  <si>
+    <t>24050068</t>
+  </si>
+  <si>
+    <t>24050069</t>
+  </si>
+  <si>
+    <t>24050070</t>
+  </si>
+  <si>
+    <t>24050071</t>
+  </si>
+  <si>
+    <t>24050072</t>
+  </si>
+  <si>
+    <t>24050073</t>
+  </si>
+  <si>
+    <t>24050074</t>
+  </si>
+  <si>
+    <t>24050075</t>
+  </si>
+  <si>
+    <t>24050076</t>
+  </si>
+  <si>
+    <t>24050077</t>
+  </si>
+  <si>
+    <t>24050078</t>
+  </si>
+  <si>
+    <t>24050079</t>
+  </si>
+  <si>
+    <t>24050080</t>
+  </si>
+  <si>
+    <t>24050081</t>
+  </si>
+  <si>
+    <t>24050083</t>
+  </si>
+  <si>
+    <t>24050084</t>
+  </si>
+  <si>
+    <t>24050086</t>
+  </si>
+  <si>
+    <t>24050087</t>
+  </si>
+  <si>
+    <t>24050088</t>
+  </si>
+  <si>
+    <t>24050089</t>
+  </si>
+  <si>
+    <t>24050090</t>
+  </si>
+  <si>
+    <t>24050091</t>
+  </si>
+  <si>
+    <t>24050093</t>
+  </si>
+  <si>
+    <t>24050094</t>
+  </si>
+  <si>
+    <t>24050095</t>
+  </si>
+  <si>
+    <t>24050097</t>
+  </si>
+  <si>
+    <t>24050098</t>
+  </si>
+  <si>
+    <t>24050099</t>
+  </si>
+  <si>
+    <t>24050100</t>
+  </si>
+  <si>
+    <t>24050101</t>
+  </si>
+  <si>
+    <t>24050102</t>
+  </si>
+  <si>
+    <t>24050104</t>
+  </si>
+  <si>
+    <t>24050106</t>
+  </si>
+  <si>
+    <t>24050107</t>
+  </si>
+  <si>
+    <t>24050111</t>
+  </si>
+  <si>
+    <t>24050112</t>
+  </si>
+  <si>
+    <t>24050113</t>
+  </si>
+  <si>
+    <t>24050114</t>
+  </si>
+  <si>
+    <t>24050115</t>
+  </si>
+  <si>
+    <t>24050117</t>
+  </si>
+  <si>
+    <t>24050118</t>
+  </si>
+  <si>
+    <t>24050121</t>
+  </si>
+  <si>
+    <t>24050122</t>
+  </si>
+  <si>
+    <t>24050123</t>
+  </si>
+  <si>
+    <t>24050125</t>
+  </si>
+  <si>
+    <t>24050126</t>
+  </si>
+  <si>
+    <t>24050127</t>
+  </si>
+  <si>
+    <t>24050128</t>
+  </si>
+  <si>
+    <t>24050129</t>
+  </si>
+  <si>
+    <t>24050130</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1920,8 +2854,37 @@
       <name val="Calibri"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF212529"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1938,6 +2901,12 @@
       <patternFill patternType="solid">
         <fgColor theme="9" tint="0.79998168889431442"/>
         <bgColor theme="9" tint="0.79998168889431442"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
@@ -2030,12 +2999,13 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -2054,11 +3024,112 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal 2" xfId="1" xr:uid="{10489084-0B01-4247-B884-6BDD41CD2F20}"/>
   </cellStyles>
-  <dxfs count="17">
+  <dxfs count="26">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <fill>
         <patternFill patternType="solid">
@@ -2252,25 +3323,25 @@
   </dxfs>
   <tableStyles count="2" defaultTableStyle="TableStylePreset3_Accent1" defaultPivotStyle="PivotStylePreset2_Accent1">
     <tableStyle name="TableStylePreset3_Accent1" pivot="0" count="7" xr9:uid="{00000000-0011-0000-FFFF-FFFF00000000}">
-      <tableStyleElement type="wholeTable" dxfId="16"/>
-      <tableStyleElement type="headerRow" dxfId="15"/>
-      <tableStyleElement type="totalRow" dxfId="14"/>
-      <tableStyleElement type="firstColumn" dxfId="13"/>
-      <tableStyleElement type="lastColumn" dxfId="12"/>
-      <tableStyleElement type="firstRowStripe" dxfId="11"/>
-      <tableStyleElement type="firstColumnStripe" dxfId="10"/>
+      <tableStyleElement type="wholeTable" dxfId="25"/>
+      <tableStyleElement type="headerRow" dxfId="24"/>
+      <tableStyleElement type="totalRow" dxfId="23"/>
+      <tableStyleElement type="firstColumn" dxfId="22"/>
+      <tableStyleElement type="lastColumn" dxfId="21"/>
+      <tableStyleElement type="firstRowStripe" dxfId="20"/>
+      <tableStyleElement type="firstColumnStripe" dxfId="19"/>
     </tableStyle>
     <tableStyle name="PivotStylePreset2_Accent1" table="0" count="10" xr9:uid="{00000000-0011-0000-FFFF-FFFF01000000}">
-      <tableStyleElement type="headerRow" dxfId="9"/>
-      <tableStyleElement type="totalRow" dxfId="8"/>
-      <tableStyleElement type="firstRowStripe" dxfId="7"/>
-      <tableStyleElement type="firstColumnStripe" dxfId="6"/>
-      <tableStyleElement type="firstSubtotalRow" dxfId="5"/>
-      <tableStyleElement type="secondSubtotalRow" dxfId="4"/>
-      <tableStyleElement type="firstRowSubheading" dxfId="3"/>
-      <tableStyleElement type="secondRowSubheading" dxfId="2"/>
-      <tableStyleElement type="pageFieldLabels" dxfId="1"/>
-      <tableStyleElement type="pageFieldValues" dxfId="0"/>
+      <tableStyleElement type="headerRow" dxfId="18"/>
+      <tableStyleElement type="totalRow" dxfId="17"/>
+      <tableStyleElement type="firstRowStripe" dxfId="16"/>
+      <tableStyleElement type="firstColumnStripe" dxfId="15"/>
+      <tableStyleElement type="firstSubtotalRow" dxfId="14"/>
+      <tableStyleElement type="secondSubtotalRow" dxfId="13"/>
+      <tableStyleElement type="firstRowSubheading" dxfId="12"/>
+      <tableStyleElement type="secondRowSubheading" dxfId="11"/>
+      <tableStyleElement type="pageFieldLabels" dxfId="10"/>
+      <tableStyleElement type="pageFieldValues" dxfId="9"/>
     </tableStyle>
   </tableStyles>
   <extLst>
@@ -2542,7 +3613,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G2199"/>
+  <dimension ref="A1:G2505"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="21.1640625" customWidth="1"/>
@@ -53129,7 +54200,7069 @@
         <v>577</v>
       </c>
     </row>
+    <row r="2200" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A2200" s="12" t="s">
+        <v>624</v>
+      </c>
+      <c r="B2200" s="10" t="s">
+        <v>127</v>
+      </c>
+      <c r="C2200" s="10" t="s">
+        <v>74</v>
+      </c>
+      <c r="D2200" s="4" t="s">
+        <v>574</v>
+      </c>
+      <c r="E2200" s="11">
+        <v>3</v>
+      </c>
+      <c r="F2200">
+        <v>69</v>
+      </c>
+      <c r="G2200" t="s">
+        <v>575</v>
+      </c>
+    </row>
+    <row r="2201" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A2201" s="12" t="s">
+        <v>625</v>
+      </c>
+      <c r="B2201" s="10" t="s">
+        <v>626</v>
+      </c>
+      <c r="C2201" s="10" t="s">
+        <v>74</v>
+      </c>
+      <c r="D2201" s="4" t="s">
+        <v>574</v>
+      </c>
+      <c r="E2201" s="11">
+        <v>3</v>
+      </c>
+      <c r="F2201">
+        <v>70</v>
+      </c>
+      <c r="G2201" t="s">
+        <v>575</v>
+      </c>
+    </row>
+    <row r="2202" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A2202" s="12" t="s">
+        <v>627</v>
+      </c>
+      <c r="B2202" s="10" t="s">
+        <v>102</v>
+      </c>
+      <c r="C2202" s="10" t="s">
+        <v>74</v>
+      </c>
+      <c r="D2202" s="4" t="s">
+        <v>574</v>
+      </c>
+      <c r="E2202" s="11">
+        <v>3</v>
+      </c>
+      <c r="F2202">
+        <v>70</v>
+      </c>
+      <c r="G2202" t="s">
+        <v>575</v>
+      </c>
+    </row>
+    <row r="2203" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A2203" s="12" t="s">
+        <v>628</v>
+      </c>
+      <c r="B2203" s="10" t="s">
+        <v>99</v>
+      </c>
+      <c r="C2203" s="10" t="s">
+        <v>74</v>
+      </c>
+      <c r="D2203" s="4" t="s">
+        <v>574</v>
+      </c>
+      <c r="E2203" s="11">
+        <v>3</v>
+      </c>
+      <c r="F2203">
+        <v>70</v>
+      </c>
+      <c r="G2203" t="s">
+        <v>575</v>
+      </c>
+    </row>
+    <row r="2204" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A2204" s="12" t="s">
+        <v>629</v>
+      </c>
+      <c r="B2204" s="10" t="s">
+        <v>91</v>
+      </c>
+      <c r="C2204" s="10" t="s">
+        <v>74</v>
+      </c>
+      <c r="D2204" s="4" t="s">
+        <v>574</v>
+      </c>
+      <c r="E2204" s="11">
+        <v>3</v>
+      </c>
+      <c r="F2204">
+        <v>86</v>
+      </c>
+      <c r="G2204" t="s">
+        <v>577</v>
+      </c>
+    </row>
+    <row r="2205" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A2205" s="12" t="s">
+        <v>630</v>
+      </c>
+      <c r="B2205" s="10" t="s">
+        <v>130</v>
+      </c>
+      <c r="C2205" s="10" t="s">
+        <v>74</v>
+      </c>
+      <c r="D2205" s="4" t="s">
+        <v>574</v>
+      </c>
+      <c r="E2205" s="11">
+        <v>3</v>
+      </c>
+      <c r="F2205">
+        <v>78</v>
+      </c>
+      <c r="G2205" t="s">
+        <v>575</v>
+      </c>
+    </row>
+    <row r="2206" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A2206" s="12" t="s">
+        <v>631</v>
+      </c>
+      <c r="B2206" s="10" t="s">
+        <v>79</v>
+      </c>
+      <c r="C2206" s="10" t="s">
+        <v>74</v>
+      </c>
+      <c r="D2206" s="4" t="s">
+        <v>574</v>
+      </c>
+      <c r="E2206" s="11">
+        <v>3</v>
+      </c>
+      <c r="F2206">
+        <v>70</v>
+      </c>
+      <c r="G2206" t="s">
+        <v>575</v>
+      </c>
+    </row>
+    <row r="2207" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A2207" s="12" t="s">
+        <v>632</v>
+      </c>
+      <c r="B2207" s="10" t="s">
+        <v>82</v>
+      </c>
+      <c r="C2207" s="10" t="s">
+        <v>74</v>
+      </c>
+      <c r="D2207" s="4" t="s">
+        <v>574</v>
+      </c>
+      <c r="E2207" s="11">
+        <v>3</v>
+      </c>
+      <c r="F2207">
+        <v>70</v>
+      </c>
+      <c r="G2207" t="s">
+        <v>575</v>
+      </c>
+    </row>
+    <row r="2208" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A2208" s="12" t="s">
+        <v>633</v>
+      </c>
+      <c r="B2208" s="10" t="s">
+        <v>77</v>
+      </c>
+      <c r="C2208" s="10" t="s">
+        <v>74</v>
+      </c>
+      <c r="D2208" s="4" t="s">
+        <v>574</v>
+      </c>
+      <c r="E2208" s="11">
+        <v>3</v>
+      </c>
+      <c r="F2208">
+        <v>70</v>
+      </c>
+      <c r="G2208" t="s">
+        <v>575</v>
+      </c>
+    </row>
+    <row r="2209" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A2209" s="12" t="s">
+        <v>634</v>
+      </c>
+      <c r="B2209" s="10" t="s">
+        <v>123</v>
+      </c>
+      <c r="C2209" s="10" t="s">
+        <v>74</v>
+      </c>
+      <c r="D2209" s="4" t="s">
+        <v>574</v>
+      </c>
+      <c r="E2209" s="11">
+        <v>3</v>
+      </c>
+      <c r="F2209">
+        <v>100</v>
+      </c>
+      <c r="G2209" t="s">
+        <v>593</v>
+      </c>
+    </row>
+    <row r="2210" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A2210" s="12" t="s">
+        <v>635</v>
+      </c>
+      <c r="B2210" s="10" t="s">
+        <v>100</v>
+      </c>
+      <c r="C2210" s="10" t="s">
+        <v>74</v>
+      </c>
+      <c r="D2210" s="4" t="s">
+        <v>574</v>
+      </c>
+      <c r="E2210" s="11">
+        <v>3</v>
+      </c>
+      <c r="F2210">
+        <v>55</v>
+      </c>
+      <c r="G2210" t="s">
+        <v>579</v>
+      </c>
+    </row>
+    <row r="2211" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A2211" s="12" t="s">
+        <v>636</v>
+      </c>
+      <c r="B2211" s="10" t="s">
+        <v>559</v>
+      </c>
+      <c r="C2211" s="10" t="s">
+        <v>74</v>
+      </c>
+      <c r="D2211" s="4" t="s">
+        <v>574</v>
+      </c>
+      <c r="E2211" s="11">
+        <v>3</v>
+      </c>
+      <c r="F2211">
+        <v>98</v>
+      </c>
+      <c r="G2211" t="s">
+        <v>593</v>
+      </c>
+    </row>
+    <row r="2212" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A2212" s="12" t="s">
+        <v>637</v>
+      </c>
+      <c r="B2212" s="10" t="s">
+        <v>558</v>
+      </c>
+      <c r="C2212" s="10" t="s">
+        <v>74</v>
+      </c>
+      <c r="D2212" s="4" t="s">
+        <v>574</v>
+      </c>
+      <c r="E2212" s="11">
+        <v>3</v>
+      </c>
+      <c r="F2212">
+        <v>70</v>
+      </c>
+      <c r="G2212" t="s">
+        <v>575</v>
+      </c>
+    </row>
+    <row r="2213" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A2213" s="12" t="s">
+        <v>638</v>
+      </c>
+      <c r="B2213" s="10" t="s">
+        <v>132</v>
+      </c>
+      <c r="C2213" s="10" t="s">
+        <v>74</v>
+      </c>
+      <c r="D2213" s="4" t="s">
+        <v>574</v>
+      </c>
+      <c r="E2213" s="11">
+        <v>3</v>
+      </c>
+      <c r="F2213">
+        <v>100</v>
+      </c>
+      <c r="G2213" t="s">
+        <v>593</v>
+      </c>
+    </row>
+    <row r="2214" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A2214" s="12" t="s">
+        <v>639</v>
+      </c>
+      <c r="B2214" s="10" t="s">
+        <v>173</v>
+      </c>
+      <c r="C2214" s="10" t="s">
+        <v>74</v>
+      </c>
+      <c r="D2214" s="4" t="s">
+        <v>574</v>
+      </c>
+      <c r="E2214" s="11">
+        <v>3</v>
+      </c>
+      <c r="F2214">
+        <v>74</v>
+      </c>
+      <c r="G2214" t="s">
+        <v>575</v>
+      </c>
+    </row>
+    <row r="2215" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A2215" s="12" t="s">
+        <v>640</v>
+      </c>
+      <c r="B2215" s="10" t="s">
+        <v>73</v>
+      </c>
+      <c r="C2215" s="10" t="s">
+        <v>74</v>
+      </c>
+      <c r="D2215" s="4" t="s">
+        <v>574</v>
+      </c>
+      <c r="E2215" s="11">
+        <v>3</v>
+      </c>
+      <c r="F2215">
+        <v>80</v>
+      </c>
+      <c r="G2215" t="s">
+        <v>577</v>
+      </c>
+    </row>
+    <row r="2216" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A2216" s="12" t="s">
+        <v>641</v>
+      </c>
+      <c r="B2216" s="10" t="s">
+        <v>557</v>
+      </c>
+      <c r="C2216" s="10" t="s">
+        <v>74</v>
+      </c>
+      <c r="D2216" s="4" t="s">
+        <v>574</v>
+      </c>
+      <c r="E2216" s="11">
+        <v>3</v>
+      </c>
+      <c r="F2216">
+        <v>99</v>
+      </c>
+      <c r="G2216" t="s">
+        <v>593</v>
+      </c>
+    </row>
+    <row r="2217" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A2217" s="12" t="s">
+        <v>642</v>
+      </c>
+      <c r="B2217" s="10" t="s">
+        <v>556</v>
+      </c>
+      <c r="C2217" s="10" t="s">
+        <v>74</v>
+      </c>
+      <c r="D2217" s="4" t="s">
+        <v>574</v>
+      </c>
+      <c r="E2217" s="11">
+        <v>3</v>
+      </c>
+      <c r="F2217">
+        <v>70</v>
+      </c>
+      <c r="G2217" t="s">
+        <v>575</v>
+      </c>
+    </row>
+    <row r="2218" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A2218" s="12" t="s">
+        <v>643</v>
+      </c>
+      <c r="B2218" s="10" t="s">
+        <v>158</v>
+      </c>
+      <c r="C2218" s="10" t="s">
+        <v>74</v>
+      </c>
+      <c r="D2218" s="4" t="s">
+        <v>574</v>
+      </c>
+      <c r="E2218" s="11">
+        <v>3</v>
+      </c>
+      <c r="F2218">
+        <v>70</v>
+      </c>
+      <c r="G2218" t="s">
+        <v>575</v>
+      </c>
+    </row>
+    <row r="2219" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A2219" s="12" t="s">
+        <v>644</v>
+      </c>
+      <c r="B2219" s="10" t="s">
+        <v>108</v>
+      </c>
+      <c r="C2219" s="10" t="s">
+        <v>74</v>
+      </c>
+      <c r="D2219" s="4" t="s">
+        <v>574</v>
+      </c>
+      <c r="E2219" s="11">
+        <v>3</v>
+      </c>
+      <c r="F2219">
+        <v>70</v>
+      </c>
+      <c r="G2219" t="s">
+        <v>575</v>
+      </c>
+    </row>
+    <row r="2220" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A2220" s="12" t="s">
+        <v>645</v>
+      </c>
+      <c r="B2220" s="10" t="s">
+        <v>88</v>
+      </c>
+      <c r="C2220" s="10" t="s">
+        <v>74</v>
+      </c>
+      <c r="D2220" s="4" t="s">
+        <v>574</v>
+      </c>
+      <c r="E2220" s="11">
+        <v>3</v>
+      </c>
+      <c r="F2220">
+        <v>70</v>
+      </c>
+      <c r="G2220" t="s">
+        <v>575</v>
+      </c>
+    </row>
+    <row r="2221" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A2221" s="12" t="s">
+        <v>646</v>
+      </c>
+      <c r="B2221" s="10" t="s">
+        <v>555</v>
+      </c>
+      <c r="C2221" s="10" t="s">
+        <v>74</v>
+      </c>
+      <c r="D2221" s="4" t="s">
+        <v>574</v>
+      </c>
+      <c r="E2221" s="11">
+        <v>3</v>
+      </c>
+      <c r="F2221">
+        <v>70</v>
+      </c>
+      <c r="G2221" t="s">
+        <v>575</v>
+      </c>
+    </row>
+    <row r="2222" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A2222" s="12" t="s">
+        <v>647</v>
+      </c>
+      <c r="B2222" s="10" t="s">
+        <v>78</v>
+      </c>
+      <c r="C2222" s="10" t="s">
+        <v>74</v>
+      </c>
+      <c r="D2222" s="4" t="s">
+        <v>574</v>
+      </c>
+      <c r="E2222" s="11">
+        <v>3</v>
+      </c>
+      <c r="F2222">
+        <v>70</v>
+      </c>
+      <c r="G2222" t="s">
+        <v>575</v>
+      </c>
+    </row>
+    <row r="2223" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A2223" s="12" t="s">
+        <v>648</v>
+      </c>
+      <c r="B2223" s="10" t="s">
+        <v>111</v>
+      </c>
+      <c r="C2223" s="10" t="s">
+        <v>74</v>
+      </c>
+      <c r="D2223" s="4" t="s">
+        <v>574</v>
+      </c>
+      <c r="E2223" s="11">
+        <v>3</v>
+      </c>
+      <c r="F2223">
+        <v>70</v>
+      </c>
+      <c r="G2223" t="s">
+        <v>575</v>
+      </c>
+    </row>
+    <row r="2224" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A2224" s="12" t="s">
+        <v>649</v>
+      </c>
+      <c r="B2224" s="10" t="s">
+        <v>554</v>
+      </c>
+      <c r="C2224" s="10" t="s">
+        <v>74</v>
+      </c>
+      <c r="D2224" s="4" t="s">
+        <v>574</v>
+      </c>
+      <c r="E2224" s="11">
+        <v>3</v>
+      </c>
+      <c r="F2224">
+        <v>93</v>
+      </c>
+      <c r="G2224" t="s">
+        <v>593</v>
+      </c>
+    </row>
+    <row r="2225" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A2225" s="12" t="s">
+        <v>650</v>
+      </c>
+      <c r="B2225" s="10" t="s">
+        <v>96</v>
+      </c>
+      <c r="C2225" s="10" t="s">
+        <v>74</v>
+      </c>
+      <c r="D2225" s="4" t="s">
+        <v>574</v>
+      </c>
+      <c r="E2225" s="11">
+        <v>3</v>
+      </c>
+      <c r="F2225">
+        <v>69</v>
+      </c>
+      <c r="G2225" t="s">
+        <v>575</v>
+      </c>
+    </row>
+    <row r="2226" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A2226" s="12" t="s">
+        <v>651</v>
+      </c>
+      <c r="B2226" s="10" t="s">
+        <v>116</v>
+      </c>
+      <c r="C2226" s="10" t="s">
+        <v>74</v>
+      </c>
+      <c r="D2226" s="4" t="s">
+        <v>574</v>
+      </c>
+      <c r="E2226" s="11">
+        <v>3</v>
+      </c>
+      <c r="F2226">
+        <v>98</v>
+      </c>
+      <c r="G2226" t="s">
+        <v>593</v>
+      </c>
+    </row>
+    <row r="2227" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A2227" s="12" t="s">
+        <v>652</v>
+      </c>
+      <c r="B2227" s="10" t="s">
+        <v>364</v>
+      </c>
+      <c r="C2227" s="10" t="s">
+        <v>74</v>
+      </c>
+      <c r="D2227" s="4" t="s">
+        <v>574</v>
+      </c>
+      <c r="E2227" s="11">
+        <v>3</v>
+      </c>
+      <c r="F2227">
+        <v>70</v>
+      </c>
+      <c r="G2227" t="s">
+        <v>575</v>
+      </c>
+    </row>
+    <row r="2228" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A2228" s="12" t="s">
+        <v>653</v>
+      </c>
+      <c r="B2228" s="10" t="s">
+        <v>84</v>
+      </c>
+      <c r="C2228" s="10" t="s">
+        <v>74</v>
+      </c>
+      <c r="D2228" s="4" t="s">
+        <v>574</v>
+      </c>
+      <c r="E2228" s="11">
+        <v>3</v>
+      </c>
+      <c r="F2228">
+        <v>70</v>
+      </c>
+      <c r="G2228" t="s">
+        <v>575</v>
+      </c>
+    </row>
+    <row r="2229" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A2229" s="12" t="s">
+        <v>654</v>
+      </c>
+      <c r="B2229" s="10" t="s">
+        <v>365</v>
+      </c>
+      <c r="C2229" s="10" t="s">
+        <v>74</v>
+      </c>
+      <c r="D2229" s="4" t="s">
+        <v>574</v>
+      </c>
+      <c r="E2229" s="11">
+        <v>3</v>
+      </c>
+      <c r="F2229">
+        <v>70</v>
+      </c>
+      <c r="G2229" t="s">
+        <v>575</v>
+      </c>
+    </row>
+    <row r="2230" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A2230" s="12" t="s">
+        <v>655</v>
+      </c>
+      <c r="B2230" s="10" t="s">
+        <v>133</v>
+      </c>
+      <c r="C2230" s="10" t="s">
+        <v>74</v>
+      </c>
+      <c r="D2230" s="4" t="s">
+        <v>574</v>
+      </c>
+      <c r="E2230" s="11">
+        <v>3</v>
+      </c>
+      <c r="F2230">
+        <v>70</v>
+      </c>
+      <c r="G2230" t="s">
+        <v>575</v>
+      </c>
+    </row>
+    <row r="2231" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A2231" s="12" t="s">
+        <v>656</v>
+      </c>
+      <c r="B2231" s="10" t="s">
+        <v>134</v>
+      </c>
+      <c r="C2231" s="10" t="s">
+        <v>74</v>
+      </c>
+      <c r="D2231" s="4" t="s">
+        <v>574</v>
+      </c>
+      <c r="E2231" s="11">
+        <v>3</v>
+      </c>
+      <c r="F2231">
+        <v>70</v>
+      </c>
+      <c r="G2231" t="s">
+        <v>575</v>
+      </c>
+    </row>
+    <row r="2232" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A2232" s="12" t="s">
+        <v>657</v>
+      </c>
+      <c r="B2232" s="10" t="s">
+        <v>143</v>
+      </c>
+      <c r="C2232" s="10" t="s">
+        <v>74</v>
+      </c>
+      <c r="D2232" s="4" t="s">
+        <v>574</v>
+      </c>
+      <c r="E2232" s="11">
+        <v>3</v>
+      </c>
+      <c r="F2232">
+        <v>70</v>
+      </c>
+      <c r="G2232" t="s">
+        <v>575</v>
+      </c>
+    </row>
+    <row r="2233" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A2233" s="12" t="s">
+        <v>658</v>
+      </c>
+      <c r="B2233" s="10" t="s">
+        <v>141</v>
+      </c>
+      <c r="C2233" s="10" t="s">
+        <v>573</v>
+      </c>
+      <c r="D2233" s="4" t="s">
+        <v>574</v>
+      </c>
+      <c r="E2233" s="11">
+        <v>3</v>
+      </c>
+      <c r="F2233">
+        <v>70</v>
+      </c>
+      <c r="G2233" t="s">
+        <v>575</v>
+      </c>
+    </row>
+    <row r="2234" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A2234" s="12" t="s">
+        <v>659</v>
+      </c>
+      <c r="B2234" s="10" t="s">
+        <v>167</v>
+      </c>
+      <c r="C2234" s="10" t="s">
+        <v>573</v>
+      </c>
+      <c r="D2234" s="4" t="s">
+        <v>574</v>
+      </c>
+      <c r="E2234" s="11">
+        <v>3</v>
+      </c>
+      <c r="F2234">
+        <v>96</v>
+      </c>
+      <c r="G2234" t="s">
+        <v>593</v>
+      </c>
+    </row>
+    <row r="2235" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A2235" s="12" t="s">
+        <v>660</v>
+      </c>
+      <c r="B2235" s="10" t="s">
+        <v>106</v>
+      </c>
+      <c r="C2235" s="10" t="s">
+        <v>573</v>
+      </c>
+      <c r="D2235" s="4" t="s">
+        <v>574</v>
+      </c>
+      <c r="E2235" s="11">
+        <v>3</v>
+      </c>
+      <c r="F2235">
+        <v>92</v>
+      </c>
+      <c r="G2235" t="s">
+        <v>593</v>
+      </c>
+    </row>
+    <row r="2236" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A2236" s="12" t="s">
+        <v>661</v>
+      </c>
+      <c r="B2236" s="10" t="s">
+        <v>87</v>
+      </c>
+      <c r="C2236" s="10" t="s">
+        <v>573</v>
+      </c>
+      <c r="D2236" s="4" t="s">
+        <v>574</v>
+      </c>
+      <c r="E2236" s="11">
+        <v>3</v>
+      </c>
+      <c r="F2236">
+        <v>70</v>
+      </c>
+      <c r="G2236" t="s">
+        <v>575</v>
+      </c>
+    </row>
+    <row r="2237" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A2237" s="12" t="s">
+        <v>662</v>
+      </c>
+      <c r="B2237" s="10" t="s">
+        <v>155</v>
+      </c>
+      <c r="C2237" s="10" t="s">
+        <v>573</v>
+      </c>
+      <c r="D2237" s="4" t="s">
+        <v>574</v>
+      </c>
+      <c r="E2237" s="11">
+        <v>3</v>
+      </c>
+      <c r="F2237">
+        <v>70</v>
+      </c>
+      <c r="G2237" t="s">
+        <v>575</v>
+      </c>
+    </row>
+    <row r="2238" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A2238" s="12" t="s">
+        <v>663</v>
+      </c>
+      <c r="B2238" s="10" t="s">
+        <v>136</v>
+      </c>
+      <c r="C2238" s="10" t="s">
+        <v>573</v>
+      </c>
+      <c r="D2238" s="4" t="s">
+        <v>574</v>
+      </c>
+      <c r="E2238" s="11">
+        <v>3</v>
+      </c>
+      <c r="F2238">
+        <v>70</v>
+      </c>
+      <c r="G2238" t="s">
+        <v>575</v>
+      </c>
+    </row>
+    <row r="2239" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A2239" s="12" t="s">
+        <v>664</v>
+      </c>
+      <c r="B2239" s="10" t="s">
+        <v>172</v>
+      </c>
+      <c r="C2239" s="10" t="s">
+        <v>573</v>
+      </c>
+      <c r="D2239" s="4" t="s">
+        <v>574</v>
+      </c>
+      <c r="E2239" s="11">
+        <v>3</v>
+      </c>
+      <c r="F2239">
+        <v>70</v>
+      </c>
+      <c r="G2239" t="s">
+        <v>575</v>
+      </c>
+    </row>
+    <row r="2240" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A2240" s="12" t="s">
+        <v>665</v>
+      </c>
+      <c r="B2240" s="10" t="s">
+        <v>103</v>
+      </c>
+      <c r="C2240" s="10" t="s">
+        <v>573</v>
+      </c>
+      <c r="D2240" s="4" t="s">
+        <v>574</v>
+      </c>
+      <c r="E2240" s="11">
+        <v>3</v>
+      </c>
+      <c r="F2240">
+        <v>55</v>
+      </c>
+      <c r="G2240" t="s">
+        <v>579</v>
+      </c>
+    </row>
+    <row r="2241" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A2241" s="12" t="s">
+        <v>666</v>
+      </c>
+      <c r="B2241" s="10" t="s">
+        <v>366</v>
+      </c>
+      <c r="C2241" s="10" t="s">
+        <v>573</v>
+      </c>
+      <c r="D2241" s="4" t="s">
+        <v>574</v>
+      </c>
+      <c r="E2241" s="11">
+        <v>3</v>
+      </c>
+      <c r="F2241">
+        <v>67</v>
+      </c>
+      <c r="G2241" t="s">
+        <v>575</v>
+      </c>
+    </row>
+    <row r="2242" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A2242" s="12" t="s">
+        <v>667</v>
+      </c>
+      <c r="B2242" s="10" t="s">
+        <v>125</v>
+      </c>
+      <c r="C2242" s="10" t="s">
+        <v>573</v>
+      </c>
+      <c r="D2242" s="4" t="s">
+        <v>574</v>
+      </c>
+      <c r="E2242" s="11">
+        <v>3</v>
+      </c>
+      <c r="F2242">
+        <v>69</v>
+      </c>
+      <c r="G2242" t="s">
+        <v>575</v>
+      </c>
+    </row>
+    <row r="2243" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A2243" s="12" t="s">
+        <v>668</v>
+      </c>
+      <c r="B2243" s="10" t="s">
+        <v>115</v>
+      </c>
+      <c r="C2243" s="10" t="s">
+        <v>573</v>
+      </c>
+      <c r="D2243" s="4" t="s">
+        <v>574</v>
+      </c>
+      <c r="E2243" s="11">
+        <v>3</v>
+      </c>
+      <c r="F2243">
+        <v>78</v>
+      </c>
+      <c r="G2243" t="s">
+        <v>575</v>
+      </c>
+    </row>
+    <row r="2244" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A2244" s="12" t="s">
+        <v>669</v>
+      </c>
+      <c r="B2244" s="10" t="s">
+        <v>587</v>
+      </c>
+      <c r="C2244" s="10" t="s">
+        <v>573</v>
+      </c>
+      <c r="D2244" s="4" t="s">
+        <v>574</v>
+      </c>
+      <c r="E2244" s="11">
+        <v>3</v>
+      </c>
+      <c r="F2244">
+        <v>70</v>
+      </c>
+      <c r="G2244" t="s">
+        <v>575</v>
+      </c>
+    </row>
+    <row r="2245" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A2245" s="12" t="s">
+        <v>670</v>
+      </c>
+      <c r="B2245" s="10" t="s">
+        <v>149</v>
+      </c>
+      <c r="C2245" s="10" t="s">
+        <v>573</v>
+      </c>
+      <c r="D2245" s="4" t="s">
+        <v>574</v>
+      </c>
+      <c r="E2245" s="11">
+        <v>3</v>
+      </c>
+      <c r="F2245">
+        <v>93</v>
+      </c>
+      <c r="G2245" t="s">
+        <v>593</v>
+      </c>
+    </row>
+    <row r="2246" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A2246" s="12" t="s">
+        <v>671</v>
+      </c>
+      <c r="B2246" s="10" t="s">
+        <v>109</v>
+      </c>
+      <c r="C2246" s="10" t="s">
+        <v>573</v>
+      </c>
+      <c r="D2246" s="4" t="s">
+        <v>574</v>
+      </c>
+      <c r="E2246" s="11">
+        <v>3</v>
+      </c>
+      <c r="F2246">
+        <v>82</v>
+      </c>
+      <c r="G2246" t="s">
+        <v>577</v>
+      </c>
+    </row>
+    <row r="2247" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A2247" s="12" t="s">
+        <v>672</v>
+      </c>
+      <c r="B2247" s="10" t="s">
+        <v>129</v>
+      </c>
+      <c r="C2247" s="10" t="s">
+        <v>573</v>
+      </c>
+      <c r="D2247" s="4" t="s">
+        <v>574</v>
+      </c>
+      <c r="E2247" s="11">
+        <v>3</v>
+      </c>
+      <c r="F2247">
+        <v>70</v>
+      </c>
+      <c r="G2247" t="s">
+        <v>575</v>
+      </c>
+    </row>
+    <row r="2248" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A2248" s="12" t="s">
+        <v>673</v>
+      </c>
+      <c r="B2248" s="10" t="s">
+        <v>98</v>
+      </c>
+      <c r="C2248" s="10" t="s">
+        <v>573</v>
+      </c>
+      <c r="D2248" s="4" t="s">
+        <v>574</v>
+      </c>
+      <c r="E2248" s="11">
+        <v>3</v>
+      </c>
+      <c r="F2248">
+        <v>100</v>
+      </c>
+      <c r="G2248" t="s">
+        <v>593</v>
+      </c>
+    </row>
+    <row r="2249" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A2249" s="12" t="s">
+        <v>674</v>
+      </c>
+      <c r="B2249" s="10" t="s">
+        <v>86</v>
+      </c>
+      <c r="C2249" s="10" t="s">
+        <v>573</v>
+      </c>
+      <c r="D2249" s="4" t="s">
+        <v>574</v>
+      </c>
+      <c r="E2249" s="11">
+        <v>3</v>
+      </c>
+      <c r="F2249">
+        <v>78</v>
+      </c>
+      <c r="G2249" t="s">
+        <v>575</v>
+      </c>
+    </row>
+    <row r="2250" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A2250" s="12" t="s">
+        <v>675</v>
+      </c>
+      <c r="B2250" s="10" t="s">
+        <v>80</v>
+      </c>
+      <c r="C2250" s="10" t="s">
+        <v>573</v>
+      </c>
+      <c r="D2250" s="4" t="s">
+        <v>574</v>
+      </c>
+      <c r="E2250" s="11">
+        <v>3</v>
+      </c>
+      <c r="F2250">
+        <v>78</v>
+      </c>
+      <c r="G2250" t="s">
+        <v>575</v>
+      </c>
+    </row>
+    <row r="2251" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A2251" s="12" t="s">
+        <v>676</v>
+      </c>
+      <c r="B2251" s="10" t="s">
+        <v>138</v>
+      </c>
+      <c r="C2251" s="10" t="s">
+        <v>573</v>
+      </c>
+      <c r="D2251" s="4" t="s">
+        <v>574</v>
+      </c>
+      <c r="E2251" s="11">
+        <v>3</v>
+      </c>
+      <c r="F2251">
+        <v>93</v>
+      </c>
+      <c r="G2251" t="s">
+        <v>593</v>
+      </c>
+    </row>
+    <row r="2252" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A2252" s="12" t="s">
+        <v>677</v>
+      </c>
+      <c r="B2252" s="10" t="s">
+        <v>110</v>
+      </c>
+      <c r="C2252" s="10" t="s">
+        <v>573</v>
+      </c>
+      <c r="D2252" s="4" t="s">
+        <v>574</v>
+      </c>
+      <c r="E2252" s="11">
+        <v>3</v>
+      </c>
+      <c r="F2252">
+        <v>70</v>
+      </c>
+      <c r="G2252" t="s">
+        <v>575</v>
+      </c>
+    </row>
+    <row r="2253" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A2253" s="12" t="s">
+        <v>678</v>
+      </c>
+      <c r="B2253" s="10" t="s">
+        <v>154</v>
+      </c>
+      <c r="C2253" s="10" t="s">
+        <v>573</v>
+      </c>
+      <c r="D2253" s="4" t="s">
+        <v>574</v>
+      </c>
+      <c r="E2253" s="11">
+        <v>3</v>
+      </c>
+      <c r="F2253">
+        <v>70</v>
+      </c>
+      <c r="G2253" t="s">
+        <v>575</v>
+      </c>
+    </row>
+    <row r="2254" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A2254" s="12" t="s">
+        <v>679</v>
+      </c>
+      <c r="B2254" s="10" t="s">
+        <v>128</v>
+      </c>
+      <c r="C2254" s="10" t="s">
+        <v>573</v>
+      </c>
+      <c r="D2254" s="4" t="s">
+        <v>574</v>
+      </c>
+      <c r="E2254" s="11">
+        <v>3</v>
+      </c>
+      <c r="F2254">
+        <v>69</v>
+      </c>
+      <c r="G2254" t="s">
+        <v>575</v>
+      </c>
+    </row>
+    <row r="2255" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A2255" s="12" t="s">
+        <v>680</v>
+      </c>
+      <c r="B2255" s="10" t="s">
+        <v>551</v>
+      </c>
+      <c r="C2255" s="10" t="s">
+        <v>573</v>
+      </c>
+      <c r="D2255" s="4" t="s">
+        <v>574</v>
+      </c>
+      <c r="E2255" s="11">
+        <v>3</v>
+      </c>
+      <c r="F2255">
+        <v>88</v>
+      </c>
+      <c r="G2255" t="s">
+        <v>577</v>
+      </c>
+    </row>
+    <row r="2256" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A2256" s="12" t="s">
+        <v>681</v>
+      </c>
+      <c r="B2256" s="10" t="s">
+        <v>552</v>
+      </c>
+      <c r="C2256" s="10" t="s">
+        <v>573</v>
+      </c>
+      <c r="D2256" s="4" t="s">
+        <v>574</v>
+      </c>
+      <c r="E2256" s="11">
+        <v>3</v>
+      </c>
+      <c r="F2256">
+        <v>96</v>
+      </c>
+      <c r="G2256" t="s">
+        <v>593</v>
+      </c>
+    </row>
+    <row r="2257" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A2257" s="12" t="s">
+        <v>682</v>
+      </c>
+      <c r="B2257" s="10" t="s">
+        <v>175</v>
+      </c>
+      <c r="C2257" s="10" t="s">
+        <v>573</v>
+      </c>
+      <c r="D2257" s="4" t="s">
+        <v>574</v>
+      </c>
+      <c r="E2257" s="11">
+        <v>3</v>
+      </c>
+      <c r="F2257">
+        <v>70</v>
+      </c>
+      <c r="G2257" t="s">
+        <v>575</v>
+      </c>
+    </row>
+    <row r="2258" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A2258" s="12" t="s">
+        <v>683</v>
+      </c>
+      <c r="B2258" s="10" t="s">
+        <v>553</v>
+      </c>
+      <c r="C2258" s="10" t="s">
+        <v>573</v>
+      </c>
+      <c r="D2258" s="4" t="s">
+        <v>574</v>
+      </c>
+      <c r="E2258" s="11">
+        <v>3</v>
+      </c>
+      <c r="F2258">
+        <v>55</v>
+      </c>
+      <c r="G2258" t="s">
+        <v>579</v>
+      </c>
+    </row>
+    <row r="2259" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A2259" s="12" t="s">
+        <v>684</v>
+      </c>
+      <c r="B2259" s="10" t="s">
+        <v>176</v>
+      </c>
+      <c r="C2259" s="10" t="s">
+        <v>573</v>
+      </c>
+      <c r="D2259" s="4" t="s">
+        <v>574</v>
+      </c>
+      <c r="E2259" s="11">
+        <v>3</v>
+      </c>
+      <c r="F2259">
+        <v>94</v>
+      </c>
+      <c r="G2259" t="s">
+        <v>593</v>
+      </c>
+    </row>
+    <row r="2260" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A2260" s="12" t="s">
+        <v>685</v>
+      </c>
+      <c r="B2260" s="10" t="s">
+        <v>165</v>
+      </c>
+      <c r="C2260" s="10" t="s">
+        <v>573</v>
+      </c>
+      <c r="D2260" s="4" t="s">
+        <v>574</v>
+      </c>
+      <c r="E2260" s="11">
+        <v>3</v>
+      </c>
+      <c r="F2260">
+        <v>69</v>
+      </c>
+      <c r="G2260" t="s">
+        <v>575</v>
+      </c>
+    </row>
+    <row r="2261" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A2261" s="12" t="s">
+        <v>686</v>
+      </c>
+      <c r="B2261" s="10" t="s">
+        <v>161</v>
+      </c>
+      <c r="C2261" s="10" t="s">
+        <v>573</v>
+      </c>
+      <c r="D2261" s="4" t="s">
+        <v>574</v>
+      </c>
+      <c r="E2261" s="11">
+        <v>3</v>
+      </c>
+      <c r="F2261">
+        <v>78</v>
+      </c>
+      <c r="G2261" t="s">
+        <v>575</v>
+      </c>
+    </row>
+    <row r="2262" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A2262" s="12" t="s">
+        <v>687</v>
+      </c>
+      <c r="B2262" s="10" t="s">
+        <v>101</v>
+      </c>
+      <c r="C2262" s="10" t="s">
+        <v>573</v>
+      </c>
+      <c r="D2262" s="4" t="s">
+        <v>574</v>
+      </c>
+      <c r="E2262" s="11">
+        <v>3</v>
+      </c>
+      <c r="F2262">
+        <v>80</v>
+      </c>
+      <c r="G2262" t="s">
+        <v>577</v>
+      </c>
+    </row>
+    <row r="2263" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A2263" s="12" t="s">
+        <v>688</v>
+      </c>
+      <c r="B2263" s="10" t="s">
+        <v>162</v>
+      </c>
+      <c r="C2263" s="10" t="s">
+        <v>573</v>
+      </c>
+      <c r="D2263" s="4" t="s">
+        <v>574</v>
+      </c>
+      <c r="E2263" s="11">
+        <v>3</v>
+      </c>
+      <c r="F2263">
+        <v>82</v>
+      </c>
+      <c r="G2263" t="s">
+        <v>577</v>
+      </c>
+    </row>
+    <row r="2264" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A2264" s="12" t="s">
+        <v>689</v>
+      </c>
+      <c r="B2264" s="10" t="s">
+        <v>83</v>
+      </c>
+      <c r="C2264" s="10" t="s">
+        <v>573</v>
+      </c>
+      <c r="D2264" s="4" t="s">
+        <v>574</v>
+      </c>
+      <c r="E2264" s="11">
+        <v>3</v>
+      </c>
+      <c r="F2264">
+        <v>70</v>
+      </c>
+      <c r="G2264" t="s">
+        <v>575</v>
+      </c>
+    </row>
+    <row r="2265" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A2265" s="12" t="s">
+        <v>690</v>
+      </c>
+      <c r="B2265" s="10" t="s">
+        <v>180</v>
+      </c>
+      <c r="C2265" s="10" t="s">
+        <v>181</v>
+      </c>
+      <c r="D2265" s="4" t="s">
+        <v>574</v>
+      </c>
+      <c r="E2265" s="11">
+        <v>3</v>
+      </c>
+      <c r="F2265">
+        <v>94</v>
+      </c>
+      <c r="G2265" t="s">
+        <v>593</v>
+      </c>
+    </row>
+    <row r="2266" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A2266" s="12" t="s">
+        <v>691</v>
+      </c>
+      <c r="B2266" s="10" t="s">
+        <v>182</v>
+      </c>
+      <c r="C2266" s="10" t="s">
+        <v>181</v>
+      </c>
+      <c r="D2266" s="4" t="s">
+        <v>574</v>
+      </c>
+      <c r="E2266" s="11">
+        <v>3</v>
+      </c>
+      <c r="F2266">
+        <v>71</v>
+      </c>
+      <c r="G2266" t="s">
+        <v>575</v>
+      </c>
+    </row>
+    <row r="2267" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A2267" s="12" t="s">
+        <v>692</v>
+      </c>
+      <c r="B2267" s="10" t="s">
+        <v>184</v>
+      </c>
+      <c r="C2267" s="10" t="s">
+        <v>181</v>
+      </c>
+      <c r="D2267" s="4" t="s">
+        <v>574</v>
+      </c>
+      <c r="E2267" s="11">
+        <v>3</v>
+      </c>
+      <c r="F2267">
+        <v>77</v>
+      </c>
+      <c r="G2267" t="s">
+        <v>575</v>
+      </c>
+    </row>
+    <row r="2268" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A2268" s="12" t="s">
+        <v>693</v>
+      </c>
+      <c r="B2268" s="10" t="s">
+        <v>185</v>
+      </c>
+      <c r="C2268" s="10" t="s">
+        <v>181</v>
+      </c>
+      <c r="D2268" s="4" t="s">
+        <v>574</v>
+      </c>
+      <c r="E2268" s="11">
+        <v>3</v>
+      </c>
+      <c r="F2268">
+        <v>91</v>
+      </c>
+      <c r="G2268" t="s">
+        <v>593</v>
+      </c>
+    </row>
+    <row r="2269" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A2269" s="12" t="s">
+        <v>694</v>
+      </c>
+      <c r="B2269" s="10" t="s">
+        <v>186</v>
+      </c>
+      <c r="C2269" s="10" t="s">
+        <v>181</v>
+      </c>
+      <c r="D2269" s="4" t="s">
+        <v>574</v>
+      </c>
+      <c r="E2269" s="11">
+        <v>3</v>
+      </c>
+      <c r="F2269">
+        <v>71</v>
+      </c>
+      <c r="G2269" t="s">
+        <v>575</v>
+      </c>
+    </row>
+    <row r="2270" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A2270" s="12" t="s">
+        <v>695</v>
+      </c>
+      <c r="B2270" s="10" t="s">
+        <v>187</v>
+      </c>
+      <c r="C2270" s="10" t="s">
+        <v>181</v>
+      </c>
+      <c r="D2270" s="4" t="s">
+        <v>574</v>
+      </c>
+      <c r="E2270" s="11">
+        <v>3</v>
+      </c>
+      <c r="F2270">
+        <v>55</v>
+      </c>
+      <c r="G2270" t="s">
+        <v>579</v>
+      </c>
+    </row>
+    <row r="2271" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A2271" s="12" t="s">
+        <v>696</v>
+      </c>
+      <c r="B2271" s="10" t="s">
+        <v>188</v>
+      </c>
+      <c r="C2271" s="10" t="s">
+        <v>181</v>
+      </c>
+      <c r="D2271" s="4" t="s">
+        <v>574</v>
+      </c>
+      <c r="E2271" s="11">
+        <v>3</v>
+      </c>
+      <c r="F2271">
+        <v>71</v>
+      </c>
+      <c r="G2271" t="s">
+        <v>575</v>
+      </c>
+    </row>
+    <row r="2272" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A2272" s="12" t="s">
+        <v>697</v>
+      </c>
+      <c r="B2272" s="10" t="s">
+        <v>190</v>
+      </c>
+      <c r="C2272" s="10" t="s">
+        <v>181</v>
+      </c>
+      <c r="D2272" s="4" t="s">
+        <v>574</v>
+      </c>
+      <c r="E2272" s="11">
+        <v>3</v>
+      </c>
+      <c r="F2272">
+        <v>99</v>
+      </c>
+      <c r="G2272" t="s">
+        <v>593</v>
+      </c>
+    </row>
+    <row r="2273" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A2273" s="12" t="s">
+        <v>698</v>
+      </c>
+      <c r="B2273" s="10" t="s">
+        <v>191</v>
+      </c>
+      <c r="C2273" s="10" t="s">
+        <v>181</v>
+      </c>
+      <c r="D2273" s="4" t="s">
+        <v>574</v>
+      </c>
+      <c r="E2273" s="11">
+        <v>3</v>
+      </c>
+      <c r="F2273">
+        <v>71</v>
+      </c>
+      <c r="G2273" t="s">
+        <v>575</v>
+      </c>
+    </row>
+    <row r="2274" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A2274" s="12" t="s">
+        <v>699</v>
+      </c>
+      <c r="B2274" s="10" t="s">
+        <v>192</v>
+      </c>
+      <c r="C2274" s="10" t="s">
+        <v>181</v>
+      </c>
+      <c r="D2274" s="4" t="s">
+        <v>574</v>
+      </c>
+      <c r="E2274" s="11">
+        <v>3</v>
+      </c>
+      <c r="F2274">
+        <v>71</v>
+      </c>
+      <c r="G2274" t="s">
+        <v>575</v>
+      </c>
+    </row>
+    <row r="2275" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A2275" s="12" t="s">
+        <v>700</v>
+      </c>
+      <c r="B2275" s="10" t="s">
+        <v>193</v>
+      </c>
+      <c r="C2275" s="10" t="s">
+        <v>181</v>
+      </c>
+      <c r="D2275" s="4" t="s">
+        <v>574</v>
+      </c>
+      <c r="E2275" s="11">
+        <v>3</v>
+      </c>
+      <c r="F2275">
+        <v>88</v>
+      </c>
+      <c r="G2275" t="s">
+        <v>577</v>
+      </c>
+    </row>
+    <row r="2276" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A2276" s="12" t="s">
+        <v>701</v>
+      </c>
+      <c r="B2276" s="10" t="s">
+        <v>194</v>
+      </c>
+      <c r="C2276" s="10" t="s">
+        <v>181</v>
+      </c>
+      <c r="D2276" s="4" t="s">
+        <v>574</v>
+      </c>
+      <c r="E2276" s="11">
+        <v>3</v>
+      </c>
+      <c r="F2276">
+        <v>74</v>
+      </c>
+      <c r="G2276" t="s">
+        <v>575</v>
+      </c>
+    </row>
+    <row r="2277" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A2277" s="12" t="s">
+        <v>702</v>
+      </c>
+      <c r="B2277" s="10" t="s">
+        <v>195</v>
+      </c>
+      <c r="C2277" s="10" t="s">
+        <v>181</v>
+      </c>
+      <c r="D2277" s="4" t="s">
+        <v>574</v>
+      </c>
+      <c r="E2277" s="11">
+        <v>3</v>
+      </c>
+      <c r="F2277">
+        <v>78</v>
+      </c>
+      <c r="G2277" t="s">
+        <v>575</v>
+      </c>
+    </row>
+    <row r="2278" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A2278" s="12" t="s">
+        <v>703</v>
+      </c>
+      <c r="B2278" s="10" t="s">
+        <v>196</v>
+      </c>
+      <c r="C2278" s="10" t="s">
+        <v>181</v>
+      </c>
+      <c r="D2278" s="4" t="s">
+        <v>574</v>
+      </c>
+      <c r="E2278" s="11">
+        <v>3</v>
+      </c>
+      <c r="F2278">
+        <v>73</v>
+      </c>
+      <c r="G2278" t="s">
+        <v>575</v>
+      </c>
+    </row>
+    <row r="2279" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A2279" s="12" t="s">
+        <v>704</v>
+      </c>
+      <c r="B2279" s="10" t="s">
+        <v>197</v>
+      </c>
+      <c r="C2279" s="10" t="s">
+        <v>181</v>
+      </c>
+      <c r="D2279" s="4" t="s">
+        <v>574</v>
+      </c>
+      <c r="E2279" s="11">
+        <v>3</v>
+      </c>
+      <c r="F2279">
+        <v>55</v>
+      </c>
+      <c r="G2279" t="s">
+        <v>579</v>
+      </c>
+    </row>
+    <row r="2280" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A2280" s="12" t="s">
+        <v>705</v>
+      </c>
+      <c r="B2280" s="10" t="s">
+        <v>198</v>
+      </c>
+      <c r="C2280" s="10" t="s">
+        <v>181</v>
+      </c>
+      <c r="D2280" s="4" t="s">
+        <v>574</v>
+      </c>
+      <c r="E2280" s="11">
+        <v>3</v>
+      </c>
+      <c r="F2280">
+        <v>71</v>
+      </c>
+      <c r="G2280" t="s">
+        <v>575</v>
+      </c>
+    </row>
+    <row r="2281" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A2281" s="12" t="s">
+        <v>706</v>
+      </c>
+      <c r="B2281" s="10" t="s">
+        <v>199</v>
+      </c>
+      <c r="C2281" s="10" t="s">
+        <v>181</v>
+      </c>
+      <c r="D2281" s="4" t="s">
+        <v>574</v>
+      </c>
+      <c r="E2281" s="11">
+        <v>3</v>
+      </c>
+      <c r="F2281">
+        <v>69</v>
+      </c>
+      <c r="G2281" t="s">
+        <v>575</v>
+      </c>
+    </row>
+    <row r="2282" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A2282" s="12" t="s">
+        <v>707</v>
+      </c>
+      <c r="B2282" s="10" t="s">
+        <v>200</v>
+      </c>
+      <c r="C2282" s="10" t="s">
+        <v>181</v>
+      </c>
+      <c r="D2282" s="4" t="s">
+        <v>574</v>
+      </c>
+      <c r="E2282" s="11">
+        <v>3</v>
+      </c>
+      <c r="F2282">
+        <v>83</v>
+      </c>
+      <c r="G2282" t="s">
+        <v>577</v>
+      </c>
+    </row>
+    <row r="2283" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A2283" s="12" t="s">
+        <v>708</v>
+      </c>
+      <c r="B2283" s="10" t="s">
+        <v>204</v>
+      </c>
+      <c r="C2283" s="10" t="s">
+        <v>181</v>
+      </c>
+      <c r="D2283" s="4" t="s">
+        <v>574</v>
+      </c>
+      <c r="E2283" s="11">
+        <v>3</v>
+      </c>
+      <c r="F2283">
+        <v>69</v>
+      </c>
+      <c r="G2283" t="s">
+        <v>575</v>
+      </c>
+    </row>
+    <row r="2284" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A2284" s="12" t="s">
+        <v>709</v>
+      </c>
+      <c r="B2284" s="10" t="s">
+        <v>205</v>
+      </c>
+      <c r="C2284" s="10" t="s">
+        <v>181</v>
+      </c>
+      <c r="D2284" s="4" t="s">
+        <v>574</v>
+      </c>
+      <c r="E2284" s="11">
+        <v>3</v>
+      </c>
+      <c r="F2284">
+        <v>67</v>
+      </c>
+      <c r="G2284" t="s">
+        <v>575</v>
+      </c>
+    </row>
+    <row r="2285" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A2285" s="12" t="s">
+        <v>710</v>
+      </c>
+      <c r="B2285" s="10" t="s">
+        <v>207</v>
+      </c>
+      <c r="C2285" s="10" t="s">
+        <v>181</v>
+      </c>
+      <c r="D2285" s="4" t="s">
+        <v>574</v>
+      </c>
+      <c r="E2285" s="11">
+        <v>3</v>
+      </c>
+      <c r="F2285">
+        <v>75</v>
+      </c>
+      <c r="G2285" t="s">
+        <v>575</v>
+      </c>
+    </row>
+    <row r="2286" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A2286" s="12" t="s">
+        <v>711</v>
+      </c>
+      <c r="B2286" s="10" t="s">
+        <v>208</v>
+      </c>
+      <c r="C2286" s="10" t="s">
+        <v>181</v>
+      </c>
+      <c r="D2286" s="4" t="s">
+        <v>574</v>
+      </c>
+      <c r="E2286" s="11">
+        <v>3</v>
+      </c>
+      <c r="F2286">
+        <v>67</v>
+      </c>
+      <c r="G2286" t="s">
+        <v>575</v>
+      </c>
+    </row>
+    <row r="2287" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A2287" s="12" t="s">
+        <v>712</v>
+      </c>
+      <c r="B2287" s="10" t="s">
+        <v>209</v>
+      </c>
+      <c r="C2287" s="10" t="s">
+        <v>181</v>
+      </c>
+      <c r="D2287" s="4" t="s">
+        <v>574</v>
+      </c>
+      <c r="E2287" s="11">
+        <v>3</v>
+      </c>
+      <c r="F2287">
+        <v>95</v>
+      </c>
+      <c r="G2287" t="s">
+        <v>593</v>
+      </c>
+    </row>
+    <row r="2288" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A2288" s="12" t="s">
+        <v>713</v>
+      </c>
+      <c r="B2288" s="10" t="s">
+        <v>210</v>
+      </c>
+      <c r="C2288" s="10" t="s">
+        <v>181</v>
+      </c>
+      <c r="D2288" s="4" t="s">
+        <v>574</v>
+      </c>
+      <c r="E2288" s="11">
+        <v>3</v>
+      </c>
+      <c r="F2288">
+        <v>69</v>
+      </c>
+      <c r="G2288" t="s">
+        <v>575</v>
+      </c>
+    </row>
+    <row r="2289" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A2289" s="12" t="s">
+        <v>714</v>
+      </c>
+      <c r="B2289" s="10" t="s">
+        <v>211</v>
+      </c>
+      <c r="C2289" s="10" t="s">
+        <v>181</v>
+      </c>
+      <c r="D2289" s="4" t="s">
+        <v>574</v>
+      </c>
+      <c r="E2289" s="11">
+        <v>3</v>
+      </c>
+      <c r="F2289">
+        <v>78</v>
+      </c>
+      <c r="G2289" t="s">
+        <v>575</v>
+      </c>
+    </row>
+    <row r="2290" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A2290" s="12" t="s">
+        <v>715</v>
+      </c>
+      <c r="B2290" s="10" t="s">
+        <v>212</v>
+      </c>
+      <c r="C2290" s="10" t="s">
+        <v>181</v>
+      </c>
+      <c r="D2290" s="4" t="s">
+        <v>574</v>
+      </c>
+      <c r="E2290" s="11">
+        <v>3</v>
+      </c>
+      <c r="F2290">
+        <v>93</v>
+      </c>
+      <c r="G2290" t="s">
+        <v>593</v>
+      </c>
+    </row>
+    <row r="2291" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A2291" s="12" t="s">
+        <v>716</v>
+      </c>
+      <c r="B2291" s="10" t="s">
+        <v>215</v>
+      </c>
+      <c r="C2291" s="10" t="s">
+        <v>181</v>
+      </c>
+      <c r="D2291" s="4" t="s">
+        <v>574</v>
+      </c>
+      <c r="E2291" s="11">
+        <v>3</v>
+      </c>
+      <c r="F2291">
+        <v>93</v>
+      </c>
+      <c r="G2291" t="s">
+        <v>593</v>
+      </c>
+    </row>
+    <row r="2292" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A2292" s="12" t="s">
+        <v>717</v>
+      </c>
+      <c r="B2292" s="10" t="s">
+        <v>217</v>
+      </c>
+      <c r="C2292" s="10" t="s">
+        <v>181</v>
+      </c>
+      <c r="D2292" s="4" t="s">
+        <v>574</v>
+      </c>
+      <c r="E2292" s="11">
+        <v>3</v>
+      </c>
+      <c r="F2292">
+        <v>81</v>
+      </c>
+      <c r="G2292" t="s">
+        <v>577</v>
+      </c>
+    </row>
+    <row r="2293" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A2293" s="12" t="s">
+        <v>718</v>
+      </c>
+      <c r="B2293" s="10" t="s">
+        <v>218</v>
+      </c>
+      <c r="C2293" s="10" t="s">
+        <v>181</v>
+      </c>
+      <c r="D2293" s="4" t="s">
+        <v>574</v>
+      </c>
+      <c r="E2293" s="11">
+        <v>3</v>
+      </c>
+      <c r="F2293">
+        <v>80</v>
+      </c>
+      <c r="G2293" t="s">
+        <v>577</v>
+      </c>
+    </row>
+    <row r="2294" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A2294" s="12" t="s">
+        <v>719</v>
+      </c>
+      <c r="B2294" s="10" t="s">
+        <v>219</v>
+      </c>
+      <c r="C2294" s="10" t="s">
+        <v>181</v>
+      </c>
+      <c r="D2294" s="4" t="s">
+        <v>574</v>
+      </c>
+      <c r="E2294" s="11">
+        <v>3</v>
+      </c>
+      <c r="F2294">
+        <v>71</v>
+      </c>
+      <c r="G2294" t="s">
+        <v>575</v>
+      </c>
+    </row>
+    <row r="2295" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A2295" s="12" t="s">
+        <v>720</v>
+      </c>
+      <c r="B2295" s="10" t="s">
+        <v>220</v>
+      </c>
+      <c r="C2295" s="10" t="s">
+        <v>181</v>
+      </c>
+      <c r="D2295" s="4" t="s">
+        <v>574</v>
+      </c>
+      <c r="E2295" s="11">
+        <v>3</v>
+      </c>
+      <c r="F2295">
+        <v>81</v>
+      </c>
+      <c r="G2295" t="s">
+        <v>577</v>
+      </c>
+    </row>
+    <row r="2296" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A2296" s="12" t="s">
+        <v>721</v>
+      </c>
+      <c r="B2296" s="10" t="s">
+        <v>221</v>
+      </c>
+      <c r="C2296" s="10" t="s">
+        <v>181</v>
+      </c>
+      <c r="D2296" s="4" t="s">
+        <v>574</v>
+      </c>
+      <c r="E2296" s="11">
+        <v>3</v>
+      </c>
+      <c r="F2296">
+        <v>70</v>
+      </c>
+      <c r="G2296" t="s">
+        <v>575</v>
+      </c>
+    </row>
+    <row r="2297" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A2297" s="12" t="s">
+        <v>722</v>
+      </c>
+      <c r="B2297" s="10" t="s">
+        <v>222</v>
+      </c>
+      <c r="C2297" s="10" t="s">
+        <v>181</v>
+      </c>
+      <c r="D2297" s="4" t="s">
+        <v>574</v>
+      </c>
+      <c r="E2297" s="11">
+        <v>3</v>
+      </c>
+      <c r="F2297">
+        <v>67</v>
+      </c>
+      <c r="G2297" t="s">
+        <v>575</v>
+      </c>
+    </row>
+    <row r="2298" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A2298" s="12" t="s">
+        <v>723</v>
+      </c>
+      <c r="B2298" s="10" t="s">
+        <v>223</v>
+      </c>
+      <c r="C2298" s="10" t="s">
+        <v>181</v>
+      </c>
+      <c r="D2298" s="4" t="s">
+        <v>574</v>
+      </c>
+      <c r="E2298" s="11">
+        <v>3</v>
+      </c>
+      <c r="F2298">
+        <v>73</v>
+      </c>
+      <c r="G2298" t="s">
+        <v>575</v>
+      </c>
+    </row>
+    <row r="2299" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A2299" s="12" t="s">
+        <v>724</v>
+      </c>
+      <c r="B2299" s="10" t="s">
+        <v>224</v>
+      </c>
+      <c r="C2299" s="10" t="s">
+        <v>181</v>
+      </c>
+      <c r="D2299" s="4" t="s">
+        <v>574</v>
+      </c>
+      <c r="E2299" s="11">
+        <v>3</v>
+      </c>
+      <c r="F2299">
+        <v>95</v>
+      </c>
+      <c r="G2299" t="s">
+        <v>593</v>
+      </c>
+    </row>
+    <row r="2300" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A2300" s="12" t="s">
+        <v>725</v>
+      </c>
+      <c r="B2300" s="10" t="s">
+        <v>225</v>
+      </c>
+      <c r="C2300" s="10" t="s">
+        <v>181</v>
+      </c>
+      <c r="D2300" s="4" t="s">
+        <v>574</v>
+      </c>
+      <c r="E2300" s="11">
+        <v>3</v>
+      </c>
+      <c r="F2300">
+        <v>69</v>
+      </c>
+      <c r="G2300" t="s">
+        <v>575</v>
+      </c>
+    </row>
+    <row r="2301" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A2301" s="12" t="s">
+        <v>726</v>
+      </c>
+      <c r="B2301" s="10" t="s">
+        <v>227</v>
+      </c>
+      <c r="C2301" s="10" t="s">
+        <v>181</v>
+      </c>
+      <c r="D2301" s="4" t="s">
+        <v>574</v>
+      </c>
+      <c r="E2301" s="11">
+        <v>3</v>
+      </c>
+      <c r="F2301">
+        <v>69</v>
+      </c>
+      <c r="G2301" t="s">
+        <v>575</v>
+      </c>
+    </row>
+    <row r="2302" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A2302" s="12" t="s">
+        <v>727</v>
+      </c>
+      <c r="B2302" s="10" t="s">
+        <v>228</v>
+      </c>
+      <c r="C2302" s="10" t="s">
+        <v>181</v>
+      </c>
+      <c r="D2302" s="4" t="s">
+        <v>574</v>
+      </c>
+      <c r="E2302" s="11">
+        <v>3</v>
+      </c>
+      <c r="F2302">
+        <v>70</v>
+      </c>
+      <c r="G2302" t="s">
+        <v>575</v>
+      </c>
+    </row>
+    <row r="2303" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A2303" s="12" t="s">
+        <v>728</v>
+      </c>
+      <c r="B2303" s="10" t="s">
+        <v>230</v>
+      </c>
+      <c r="C2303" s="10" t="s">
+        <v>181</v>
+      </c>
+      <c r="D2303" s="4" t="s">
+        <v>574</v>
+      </c>
+      <c r="E2303" s="11">
+        <v>3</v>
+      </c>
+      <c r="F2303">
+        <v>67</v>
+      </c>
+      <c r="G2303" t="s">
+        <v>575</v>
+      </c>
+    </row>
+    <row r="2304" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A2304" s="12" t="s">
+        <v>729</v>
+      </c>
+      <c r="B2304" s="10" t="s">
+        <v>231</v>
+      </c>
+      <c r="C2304" s="10" t="s">
+        <v>181</v>
+      </c>
+      <c r="D2304" s="4" t="s">
+        <v>574</v>
+      </c>
+      <c r="E2304" s="11">
+        <v>3</v>
+      </c>
+      <c r="F2304">
+        <v>92</v>
+      </c>
+      <c r="G2304" t="s">
+        <v>593</v>
+      </c>
+    </row>
+    <row r="2305" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A2305" s="12" t="s">
+        <v>730</v>
+      </c>
+      <c r="B2305" s="10" t="s">
+        <v>232</v>
+      </c>
+      <c r="C2305" s="10" t="s">
+        <v>181</v>
+      </c>
+      <c r="D2305" s="4" t="s">
+        <v>574</v>
+      </c>
+      <c r="E2305" s="11">
+        <v>3</v>
+      </c>
+      <c r="F2305">
+        <v>99</v>
+      </c>
+      <c r="G2305" t="s">
+        <v>593</v>
+      </c>
+    </row>
+    <row r="2306" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A2306" s="12" t="s">
+        <v>731</v>
+      </c>
+      <c r="B2306" s="10" t="s">
+        <v>233</v>
+      </c>
+      <c r="C2306" s="10" t="s">
+        <v>181</v>
+      </c>
+      <c r="D2306" s="4" t="s">
+        <v>574</v>
+      </c>
+      <c r="E2306" s="11">
+        <v>3</v>
+      </c>
+      <c r="F2306">
+        <v>81</v>
+      </c>
+      <c r="G2306" t="s">
+        <v>577</v>
+      </c>
+    </row>
+    <row r="2307" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A2307" s="12" t="s">
+        <v>732</v>
+      </c>
+      <c r="B2307" s="10" t="s">
+        <v>238</v>
+      </c>
+      <c r="C2307" s="10" t="s">
+        <v>239</v>
+      </c>
+      <c r="D2307" s="4" t="s">
+        <v>574</v>
+      </c>
+      <c r="E2307" s="11">
+        <v>3</v>
+      </c>
+      <c r="F2307">
+        <v>70</v>
+      </c>
+      <c r="G2307" t="s">
+        <v>575</v>
+      </c>
+    </row>
+    <row r="2308" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A2308" s="12" t="s">
+        <v>733</v>
+      </c>
+      <c r="B2308" s="10" t="s">
+        <v>240</v>
+      </c>
+      <c r="C2308" s="10" t="s">
+        <v>239</v>
+      </c>
+      <c r="D2308" s="4" t="s">
+        <v>574</v>
+      </c>
+      <c r="E2308" s="11">
+        <v>3</v>
+      </c>
+      <c r="F2308">
+        <v>69</v>
+      </c>
+      <c r="G2308" t="s">
+        <v>575</v>
+      </c>
+    </row>
+    <row r="2309" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A2309" s="12" t="s">
+        <v>734</v>
+      </c>
+      <c r="B2309" s="10" t="s">
+        <v>241</v>
+      </c>
+      <c r="C2309" s="10" t="s">
+        <v>239</v>
+      </c>
+      <c r="D2309" s="4" t="s">
+        <v>574</v>
+      </c>
+      <c r="E2309" s="11">
+        <v>3</v>
+      </c>
+      <c r="F2309">
+        <v>55</v>
+      </c>
+      <c r="G2309" t="s">
+        <v>579</v>
+      </c>
+    </row>
+    <row r="2310" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A2310" s="12" t="s">
+        <v>735</v>
+      </c>
+      <c r="B2310" s="10" t="s">
+        <v>242</v>
+      </c>
+      <c r="C2310" s="10" t="s">
+        <v>239</v>
+      </c>
+      <c r="D2310" s="4" t="s">
+        <v>574</v>
+      </c>
+      <c r="E2310" s="11">
+        <v>3</v>
+      </c>
+      <c r="F2310">
+        <v>67</v>
+      </c>
+      <c r="G2310" t="s">
+        <v>575</v>
+      </c>
+    </row>
+    <row r="2311" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A2311" s="12" t="s">
+        <v>736</v>
+      </c>
+      <c r="B2311" s="10" t="s">
+        <v>243</v>
+      </c>
+      <c r="C2311" s="10" t="s">
+        <v>239</v>
+      </c>
+      <c r="D2311" s="4" t="s">
+        <v>574</v>
+      </c>
+      <c r="E2311" s="11">
+        <v>3</v>
+      </c>
+      <c r="F2311">
+        <v>85</v>
+      </c>
+      <c r="G2311" t="s">
+        <v>577</v>
+      </c>
+    </row>
+    <row r="2312" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A2312" s="12" t="s">
+        <v>737</v>
+      </c>
+      <c r="B2312" s="10" t="s">
+        <v>245</v>
+      </c>
+      <c r="C2312" s="10" t="s">
+        <v>239</v>
+      </c>
+      <c r="D2312" s="4" t="s">
+        <v>574</v>
+      </c>
+      <c r="E2312" s="11">
+        <v>3</v>
+      </c>
+      <c r="F2312">
+        <v>70</v>
+      </c>
+      <c r="G2312" t="s">
+        <v>575</v>
+      </c>
+    </row>
+    <row r="2313" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A2313" s="12" t="s">
+        <v>738</v>
+      </c>
+      <c r="B2313" s="10" t="s">
+        <v>246</v>
+      </c>
+      <c r="C2313" s="10" t="s">
+        <v>239</v>
+      </c>
+      <c r="D2313" s="4" t="s">
+        <v>574</v>
+      </c>
+      <c r="E2313" s="11">
+        <v>3</v>
+      </c>
+      <c r="F2313">
+        <v>81</v>
+      </c>
+      <c r="G2313" t="s">
+        <v>577</v>
+      </c>
+    </row>
+    <row r="2314" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A2314" s="12" t="s">
+        <v>739</v>
+      </c>
+      <c r="B2314" s="10" t="s">
+        <v>247</v>
+      </c>
+      <c r="C2314" s="10" t="s">
+        <v>239</v>
+      </c>
+      <c r="D2314" s="4" t="s">
+        <v>574</v>
+      </c>
+      <c r="E2314" s="11">
+        <v>3</v>
+      </c>
+      <c r="F2314">
+        <v>77</v>
+      </c>
+      <c r="G2314" t="s">
+        <v>575</v>
+      </c>
+    </row>
+    <row r="2315" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A2315" s="12" t="s">
+        <v>740</v>
+      </c>
+      <c r="B2315" s="10" t="s">
+        <v>248</v>
+      </c>
+      <c r="C2315" s="10" t="s">
+        <v>239</v>
+      </c>
+      <c r="D2315" s="4" t="s">
+        <v>574</v>
+      </c>
+      <c r="E2315" s="11">
+        <v>3</v>
+      </c>
+      <c r="F2315">
+        <v>70</v>
+      </c>
+      <c r="G2315" t="s">
+        <v>575</v>
+      </c>
+    </row>
+    <row r="2316" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A2316" s="12" t="s">
+        <v>741</v>
+      </c>
+      <c r="B2316" s="10" t="s">
+        <v>249</v>
+      </c>
+      <c r="C2316" s="10" t="s">
+        <v>239</v>
+      </c>
+      <c r="D2316" s="4" t="s">
+        <v>574</v>
+      </c>
+      <c r="E2316" s="11">
+        <v>3</v>
+      </c>
+      <c r="F2316">
+        <v>55</v>
+      </c>
+      <c r="G2316" t="s">
+        <v>579</v>
+      </c>
+    </row>
+    <row r="2317" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A2317" s="12" t="s">
+        <v>742</v>
+      </c>
+      <c r="B2317" s="10" t="s">
+        <v>250</v>
+      </c>
+      <c r="C2317" s="10" t="s">
+        <v>239</v>
+      </c>
+      <c r="D2317" s="4" t="s">
+        <v>574</v>
+      </c>
+      <c r="E2317" s="11">
+        <v>3</v>
+      </c>
+      <c r="F2317">
+        <v>100</v>
+      </c>
+      <c r="G2317" t="s">
+        <v>593</v>
+      </c>
+    </row>
+    <row r="2318" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A2318" s="12" t="s">
+        <v>743</v>
+      </c>
+      <c r="B2318" s="10" t="s">
+        <v>251</v>
+      </c>
+      <c r="C2318" s="10" t="s">
+        <v>239</v>
+      </c>
+      <c r="D2318" s="4" t="s">
+        <v>574</v>
+      </c>
+      <c r="E2318" s="11">
+        <v>3</v>
+      </c>
+      <c r="F2318">
+        <v>73</v>
+      </c>
+      <c r="G2318" t="s">
+        <v>575</v>
+      </c>
+    </row>
+    <row r="2319" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A2319" s="12" t="s">
+        <v>744</v>
+      </c>
+      <c r="B2319" s="10" t="s">
+        <v>252</v>
+      </c>
+      <c r="C2319" s="10" t="s">
+        <v>239</v>
+      </c>
+      <c r="D2319" s="4" t="s">
+        <v>574</v>
+      </c>
+      <c r="E2319" s="11">
+        <v>3</v>
+      </c>
+      <c r="F2319">
+        <v>74</v>
+      </c>
+      <c r="G2319" t="s">
+        <v>575</v>
+      </c>
+    </row>
+    <row r="2320" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A2320" s="12" t="s">
+        <v>745</v>
+      </c>
+      <c r="B2320" s="10" t="s">
+        <v>254</v>
+      </c>
+      <c r="C2320" s="10" t="s">
+        <v>239</v>
+      </c>
+      <c r="D2320" s="4" t="s">
+        <v>574</v>
+      </c>
+      <c r="E2320" s="11">
+        <v>3</v>
+      </c>
+      <c r="F2320">
+        <v>73</v>
+      </c>
+      <c r="G2320" t="s">
+        <v>575</v>
+      </c>
+    </row>
+    <row r="2321" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A2321" s="12" t="s">
+        <v>746</v>
+      </c>
+      <c r="B2321" s="10" t="s">
+        <v>255</v>
+      </c>
+      <c r="C2321" s="10" t="s">
+        <v>239</v>
+      </c>
+      <c r="D2321" s="4" t="s">
+        <v>574</v>
+      </c>
+      <c r="E2321" s="11">
+        <v>3</v>
+      </c>
+      <c r="F2321">
+        <v>70</v>
+      </c>
+      <c r="G2321" t="s">
+        <v>575</v>
+      </c>
+    </row>
+    <row r="2322" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A2322" s="12" t="s">
+        <v>747</v>
+      </c>
+      <c r="B2322" s="10" t="s">
+        <v>256</v>
+      </c>
+      <c r="C2322" s="10" t="s">
+        <v>239</v>
+      </c>
+      <c r="D2322" s="4" t="s">
+        <v>574</v>
+      </c>
+      <c r="E2322" s="11">
+        <v>3</v>
+      </c>
+      <c r="F2322">
+        <v>70</v>
+      </c>
+      <c r="G2322" t="s">
+        <v>575</v>
+      </c>
+    </row>
+    <row r="2323" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A2323" s="12" t="s">
+        <v>748</v>
+      </c>
+      <c r="B2323" s="10" t="s">
+        <v>257</v>
+      </c>
+      <c r="C2323" s="10" t="s">
+        <v>239</v>
+      </c>
+      <c r="D2323" s="4" t="s">
+        <v>574</v>
+      </c>
+      <c r="E2323" s="11">
+        <v>3</v>
+      </c>
+      <c r="F2323">
+        <v>73</v>
+      </c>
+      <c r="G2323" t="s">
+        <v>575</v>
+      </c>
+    </row>
+    <row r="2324" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A2324" s="12" t="s">
+        <v>749</v>
+      </c>
+      <c r="B2324" s="10" t="s">
+        <v>258</v>
+      </c>
+      <c r="C2324" s="10" t="s">
+        <v>239</v>
+      </c>
+      <c r="D2324" s="4" t="s">
+        <v>574</v>
+      </c>
+      <c r="E2324" s="11">
+        <v>3</v>
+      </c>
+      <c r="F2324">
+        <v>55</v>
+      </c>
+      <c r="G2324" t="s">
+        <v>579</v>
+      </c>
+    </row>
+    <row r="2325" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A2325" s="12" t="s">
+        <v>750</v>
+      </c>
+      <c r="B2325" s="10" t="s">
+        <v>561</v>
+      </c>
+      <c r="C2325" s="10" t="s">
+        <v>239</v>
+      </c>
+      <c r="D2325" s="4" t="s">
+        <v>574</v>
+      </c>
+      <c r="E2325" s="11">
+        <v>3</v>
+      </c>
+      <c r="F2325">
+        <v>70</v>
+      </c>
+      <c r="G2325" t="s">
+        <v>575</v>
+      </c>
+    </row>
+    <row r="2326" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A2326" s="12" t="s">
+        <v>751</v>
+      </c>
+      <c r="B2326" s="10" t="s">
+        <v>259</v>
+      </c>
+      <c r="C2326" s="10" t="s">
+        <v>239</v>
+      </c>
+      <c r="D2326" s="4" t="s">
+        <v>574</v>
+      </c>
+      <c r="E2326" s="11">
+        <v>3</v>
+      </c>
+      <c r="F2326">
+        <v>70</v>
+      </c>
+      <c r="G2326" t="s">
+        <v>575</v>
+      </c>
+    </row>
+    <row r="2327" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A2327" s="12" t="s">
+        <v>752</v>
+      </c>
+      <c r="B2327" s="10" t="s">
+        <v>260</v>
+      </c>
+      <c r="C2327" s="10" t="s">
+        <v>239</v>
+      </c>
+      <c r="D2327" s="4" t="s">
+        <v>574</v>
+      </c>
+      <c r="E2327" s="11">
+        <v>3</v>
+      </c>
+      <c r="F2327">
+        <v>70</v>
+      </c>
+      <c r="G2327" t="s">
+        <v>575</v>
+      </c>
+    </row>
+    <row r="2328" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A2328" s="12" t="s">
+        <v>753</v>
+      </c>
+      <c r="B2328" s="10" t="s">
+        <v>261</v>
+      </c>
+      <c r="C2328" s="10" t="s">
+        <v>239</v>
+      </c>
+      <c r="D2328" s="4" t="s">
+        <v>574</v>
+      </c>
+      <c r="E2328" s="11">
+        <v>3</v>
+      </c>
+      <c r="F2328">
+        <v>70</v>
+      </c>
+      <c r="G2328" t="s">
+        <v>575</v>
+      </c>
+    </row>
+    <row r="2329" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A2329" s="12" t="s">
+        <v>754</v>
+      </c>
+      <c r="B2329" s="10" t="s">
+        <v>262</v>
+      </c>
+      <c r="C2329" s="10" t="s">
+        <v>239</v>
+      </c>
+      <c r="D2329" s="4" t="s">
+        <v>574</v>
+      </c>
+      <c r="E2329" s="11">
+        <v>3</v>
+      </c>
+      <c r="F2329">
+        <v>70</v>
+      </c>
+      <c r="G2329" t="s">
+        <v>575</v>
+      </c>
+    </row>
+    <row r="2330" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A2330" s="12" t="s">
+        <v>755</v>
+      </c>
+      <c r="B2330" s="10" t="s">
+        <v>263</v>
+      </c>
+      <c r="C2330" s="10" t="s">
+        <v>239</v>
+      </c>
+      <c r="D2330" s="4" t="s">
+        <v>574</v>
+      </c>
+      <c r="E2330" s="11">
+        <v>3</v>
+      </c>
+      <c r="F2330">
+        <v>69</v>
+      </c>
+      <c r="G2330" t="s">
+        <v>575</v>
+      </c>
+    </row>
+    <row r="2331" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A2331" s="12" t="s">
+        <v>756</v>
+      </c>
+      <c r="B2331" s="10" t="s">
+        <v>264</v>
+      </c>
+      <c r="C2331" s="10" t="s">
+        <v>239</v>
+      </c>
+      <c r="D2331" s="4" t="s">
+        <v>574</v>
+      </c>
+      <c r="E2331" s="11">
+        <v>3</v>
+      </c>
+      <c r="F2331">
+        <v>55</v>
+      </c>
+      <c r="G2331" t="s">
+        <v>579</v>
+      </c>
+    </row>
+    <row r="2332" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A2332" s="12" t="s">
+        <v>757</v>
+      </c>
+      <c r="B2332" s="10" t="s">
+        <v>265</v>
+      </c>
+      <c r="C2332" s="10" t="s">
+        <v>239</v>
+      </c>
+      <c r="D2332" s="4" t="s">
+        <v>574</v>
+      </c>
+      <c r="E2332" s="11">
+        <v>3</v>
+      </c>
+      <c r="F2332">
+        <v>70</v>
+      </c>
+      <c r="G2332" t="s">
+        <v>575</v>
+      </c>
+    </row>
+    <row r="2333" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A2333" s="12" t="s">
+        <v>758</v>
+      </c>
+      <c r="B2333" s="10" t="s">
+        <v>267</v>
+      </c>
+      <c r="C2333" s="10" t="s">
+        <v>239</v>
+      </c>
+      <c r="D2333" s="4" t="s">
+        <v>574</v>
+      </c>
+      <c r="E2333" s="11">
+        <v>3</v>
+      </c>
+      <c r="F2333">
+        <v>67</v>
+      </c>
+      <c r="G2333" t="s">
+        <v>575</v>
+      </c>
+    </row>
+    <row r="2334" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A2334" s="12" t="s">
+        <v>759</v>
+      </c>
+      <c r="B2334" s="10" t="s">
+        <v>268</v>
+      </c>
+      <c r="C2334" s="10" t="s">
+        <v>239</v>
+      </c>
+      <c r="D2334" s="4" t="s">
+        <v>574</v>
+      </c>
+      <c r="E2334" s="11">
+        <v>3</v>
+      </c>
+      <c r="F2334">
+        <v>70</v>
+      </c>
+      <c r="G2334" t="s">
+        <v>575</v>
+      </c>
+    </row>
+    <row r="2335" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A2335" s="12" t="s">
+        <v>760</v>
+      </c>
+      <c r="B2335" s="10" t="s">
+        <v>269</v>
+      </c>
+      <c r="C2335" s="10" t="s">
+        <v>239</v>
+      </c>
+      <c r="D2335" s="4" t="s">
+        <v>574</v>
+      </c>
+      <c r="E2335" s="11">
+        <v>3</v>
+      </c>
+      <c r="F2335">
+        <v>69</v>
+      </c>
+      <c r="G2335" t="s">
+        <v>575</v>
+      </c>
+    </row>
+    <row r="2336" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A2336" s="12" t="s">
+        <v>761</v>
+      </c>
+      <c r="B2336" s="10" t="s">
+        <v>270</v>
+      </c>
+      <c r="C2336" s="10" t="s">
+        <v>239</v>
+      </c>
+      <c r="D2336" s="4" t="s">
+        <v>574</v>
+      </c>
+      <c r="E2336" s="11">
+        <v>3</v>
+      </c>
+      <c r="F2336">
+        <v>69</v>
+      </c>
+      <c r="G2336" t="s">
+        <v>575</v>
+      </c>
+    </row>
+    <row r="2337" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A2337" s="12" t="s">
+        <v>762</v>
+      </c>
+      <c r="B2337" s="10" t="s">
+        <v>272</v>
+      </c>
+      <c r="C2337" s="10" t="s">
+        <v>239</v>
+      </c>
+      <c r="D2337" s="4" t="s">
+        <v>574</v>
+      </c>
+      <c r="E2337" s="11">
+        <v>3</v>
+      </c>
+      <c r="F2337">
+        <v>82</v>
+      </c>
+      <c r="G2337" t="s">
+        <v>577</v>
+      </c>
+    </row>
+    <row r="2338" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A2338" s="12" t="s">
+        <v>763</v>
+      </c>
+      <c r="B2338" s="10" t="s">
+        <v>273</v>
+      </c>
+      <c r="C2338" s="10" t="s">
+        <v>239</v>
+      </c>
+      <c r="D2338" s="4" t="s">
+        <v>574</v>
+      </c>
+      <c r="E2338" s="11">
+        <v>3</v>
+      </c>
+      <c r="F2338">
+        <v>70</v>
+      </c>
+      <c r="G2338" t="s">
+        <v>575</v>
+      </c>
+    </row>
+    <row r="2339" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A2339" s="12" t="s">
+        <v>764</v>
+      </c>
+      <c r="B2339" s="10" t="s">
+        <v>274</v>
+      </c>
+      <c r="C2339" s="10" t="s">
+        <v>239</v>
+      </c>
+      <c r="D2339" s="4" t="s">
+        <v>574</v>
+      </c>
+      <c r="E2339" s="11">
+        <v>3</v>
+      </c>
+      <c r="F2339">
+        <v>69</v>
+      </c>
+      <c r="G2339" t="s">
+        <v>575</v>
+      </c>
+    </row>
+    <row r="2340" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A2340" s="12" t="s">
+        <v>765</v>
+      </c>
+      <c r="B2340" s="10" t="s">
+        <v>275</v>
+      </c>
+      <c r="C2340" s="10" t="s">
+        <v>239</v>
+      </c>
+      <c r="D2340" s="4" t="s">
+        <v>574</v>
+      </c>
+      <c r="E2340" s="11">
+        <v>3</v>
+      </c>
+      <c r="F2340">
+        <v>92</v>
+      </c>
+      <c r="G2340" t="s">
+        <v>593</v>
+      </c>
+    </row>
+    <row r="2341" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A2341" s="12" t="s">
+        <v>766</v>
+      </c>
+      <c r="B2341" s="10" t="s">
+        <v>278</v>
+      </c>
+      <c r="C2341" s="10" t="s">
+        <v>239</v>
+      </c>
+      <c r="D2341" s="4" t="s">
+        <v>574</v>
+      </c>
+      <c r="E2341" s="11">
+        <v>3</v>
+      </c>
+      <c r="F2341">
+        <v>70</v>
+      </c>
+      <c r="G2341" t="s">
+        <v>575</v>
+      </c>
+    </row>
+    <row r="2342" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A2342" s="12" t="s">
+        <v>767</v>
+      </c>
+      <c r="B2342" s="10" t="s">
+        <v>279</v>
+      </c>
+      <c r="C2342" s="10" t="s">
+        <v>239</v>
+      </c>
+      <c r="D2342" s="4" t="s">
+        <v>574</v>
+      </c>
+      <c r="E2342" s="11">
+        <v>3</v>
+      </c>
+      <c r="F2342">
+        <v>70</v>
+      </c>
+      <c r="G2342" t="s">
+        <v>575</v>
+      </c>
+    </row>
+    <row r="2343" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A2343" s="12" t="s">
+        <v>768</v>
+      </c>
+      <c r="B2343" s="10" t="s">
+        <v>280</v>
+      </c>
+      <c r="C2343" s="10" t="s">
+        <v>239</v>
+      </c>
+      <c r="D2343" s="4" t="s">
+        <v>574</v>
+      </c>
+      <c r="E2343" s="11">
+        <v>3</v>
+      </c>
+      <c r="F2343">
+        <v>70</v>
+      </c>
+      <c r="G2343" t="s">
+        <v>575</v>
+      </c>
+    </row>
+    <row r="2344" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A2344" s="12" t="s">
+        <v>769</v>
+      </c>
+      <c r="B2344" s="10" t="s">
+        <v>281</v>
+      </c>
+      <c r="C2344" s="10" t="s">
+        <v>239</v>
+      </c>
+      <c r="D2344" s="4" t="s">
+        <v>574</v>
+      </c>
+      <c r="E2344" s="11">
+        <v>3</v>
+      </c>
+      <c r="F2344">
+        <v>70</v>
+      </c>
+      <c r="G2344" t="s">
+        <v>575</v>
+      </c>
+    </row>
+    <row r="2345" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A2345" s="12" t="s">
+        <v>770</v>
+      </c>
+      <c r="B2345" s="10" t="s">
+        <v>33</v>
+      </c>
+      <c r="C2345" s="10" t="s">
+        <v>239</v>
+      </c>
+      <c r="D2345" s="4" t="s">
+        <v>574</v>
+      </c>
+      <c r="E2345" s="11">
+        <v>3</v>
+      </c>
+      <c r="F2345">
+        <v>74</v>
+      </c>
+      <c r="G2345" t="s">
+        <v>575</v>
+      </c>
+    </row>
+    <row r="2346" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A2346" s="12" t="s">
+        <v>771</v>
+      </c>
+      <c r="B2346" s="10" t="s">
+        <v>283</v>
+      </c>
+      <c r="C2346" s="10" t="s">
+        <v>239</v>
+      </c>
+      <c r="D2346" s="4" t="s">
+        <v>574</v>
+      </c>
+      <c r="E2346" s="11">
+        <v>3</v>
+      </c>
+      <c r="F2346">
+        <v>89</v>
+      </c>
+      <c r="G2346" t="s">
+        <v>577</v>
+      </c>
+    </row>
+    <row r="2347" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A2347" s="12" t="s">
+        <v>772</v>
+      </c>
+      <c r="B2347" s="10" t="s">
+        <v>284</v>
+      </c>
+      <c r="C2347" s="10" t="s">
+        <v>239</v>
+      </c>
+      <c r="D2347" s="4" t="s">
+        <v>574</v>
+      </c>
+      <c r="E2347" s="11">
+        <v>3</v>
+      </c>
+      <c r="F2347">
+        <v>93</v>
+      </c>
+      <c r="G2347" t="s">
+        <v>593</v>
+      </c>
+    </row>
+    <row r="2348" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A2348" s="12" t="s">
+        <v>773</v>
+      </c>
+      <c r="B2348" s="10" t="s">
+        <v>285</v>
+      </c>
+      <c r="C2348" s="10" t="s">
+        <v>239</v>
+      </c>
+      <c r="D2348" s="4" t="s">
+        <v>574</v>
+      </c>
+      <c r="E2348" s="11">
+        <v>3</v>
+      </c>
+      <c r="F2348">
+        <v>70</v>
+      </c>
+      <c r="G2348" t="s">
+        <v>575</v>
+      </c>
+    </row>
+    <row r="2349" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A2349" s="12" t="s">
+        <v>774</v>
+      </c>
+      <c r="B2349" s="10" t="s">
+        <v>286</v>
+      </c>
+      <c r="C2349" s="10" t="s">
+        <v>239</v>
+      </c>
+      <c r="D2349" s="4" t="s">
+        <v>574</v>
+      </c>
+      <c r="E2349" s="11">
+        <v>3</v>
+      </c>
+      <c r="F2349">
+        <v>88</v>
+      </c>
+      <c r="G2349" t="s">
+        <v>577</v>
+      </c>
+    </row>
+    <row r="2350" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A2350" s="12" t="s">
+        <v>775</v>
+      </c>
+      <c r="B2350" s="10" t="s">
+        <v>287</v>
+      </c>
+      <c r="C2350" s="10" t="s">
+        <v>239</v>
+      </c>
+      <c r="D2350" s="4" t="s">
+        <v>574</v>
+      </c>
+      <c r="E2350" s="11">
+        <v>3</v>
+      </c>
+      <c r="F2350">
+        <v>67</v>
+      </c>
+      <c r="G2350" t="s">
+        <v>575</v>
+      </c>
+    </row>
+    <row r="2351" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A2351" s="12" t="s">
+        <v>776</v>
+      </c>
+      <c r="B2351" s="10" t="s">
+        <v>288</v>
+      </c>
+      <c r="C2351" s="10" t="s">
+        <v>239</v>
+      </c>
+      <c r="D2351" s="4" t="s">
+        <v>574</v>
+      </c>
+      <c r="E2351" s="11">
+        <v>3</v>
+      </c>
+      <c r="F2351">
+        <v>69</v>
+      </c>
+      <c r="G2351" t="s">
+        <v>575</v>
+      </c>
+    </row>
+    <row r="2352" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A2352" s="12" t="s">
+        <v>777</v>
+      </c>
+      <c r="B2352" s="10" t="s">
+        <v>289</v>
+      </c>
+      <c r="C2352" s="10" t="s">
+        <v>290</v>
+      </c>
+      <c r="D2352" s="4" t="s">
+        <v>574</v>
+      </c>
+      <c r="E2352" s="11">
+        <v>3</v>
+      </c>
+      <c r="F2352">
+        <v>60</v>
+      </c>
+      <c r="G2352" t="s">
+        <v>579</v>
+      </c>
+    </row>
+    <row r="2353" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A2353" s="12" t="s">
+        <v>778</v>
+      </c>
+      <c r="B2353" s="10" t="s">
+        <v>291</v>
+      </c>
+      <c r="C2353" s="10" t="s">
+        <v>290</v>
+      </c>
+      <c r="D2353" s="4" t="s">
+        <v>574</v>
+      </c>
+      <c r="E2353" s="11">
+        <v>3</v>
+      </c>
+      <c r="F2353">
+        <v>70</v>
+      </c>
+      <c r="G2353" t="s">
+        <v>575</v>
+      </c>
+    </row>
+    <row r="2354" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A2354" s="12" t="s">
+        <v>779</v>
+      </c>
+      <c r="B2354" s="10" t="s">
+        <v>295</v>
+      </c>
+      <c r="C2354" s="10" t="s">
+        <v>290</v>
+      </c>
+      <c r="D2354" s="4" t="s">
+        <v>574</v>
+      </c>
+      <c r="E2354" s="11">
+        <v>3</v>
+      </c>
+      <c r="F2354">
+        <v>64</v>
+      </c>
+      <c r="G2354" t="s">
+        <v>579</v>
+      </c>
+    </row>
+    <row r="2355" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A2355" s="12" t="s">
+        <v>780</v>
+      </c>
+      <c r="B2355" s="10" t="s">
+        <v>296</v>
+      </c>
+      <c r="C2355" s="10" t="s">
+        <v>290</v>
+      </c>
+      <c r="D2355" s="4" t="s">
+        <v>574</v>
+      </c>
+      <c r="E2355" s="11">
+        <v>3</v>
+      </c>
+      <c r="F2355">
+        <v>65</v>
+      </c>
+      <c r="G2355" t="s">
+        <v>575</v>
+      </c>
+    </row>
+    <row r="2356" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A2356" s="12" t="s">
+        <v>781</v>
+      </c>
+      <c r="B2356" s="10" t="s">
+        <v>297</v>
+      </c>
+      <c r="C2356" s="10" t="s">
+        <v>290</v>
+      </c>
+      <c r="D2356" s="4" t="s">
+        <v>574</v>
+      </c>
+      <c r="E2356" s="11">
+        <v>3</v>
+      </c>
+      <c r="F2356">
+        <v>50</v>
+      </c>
+      <c r="G2356" t="s">
+        <v>579</v>
+      </c>
+    </row>
+    <row r="2357" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A2357" s="12" t="s">
+        <v>782</v>
+      </c>
+      <c r="B2357" s="10" t="s">
+        <v>298</v>
+      </c>
+      <c r="C2357" s="10" t="s">
+        <v>290</v>
+      </c>
+      <c r="D2357" s="4" t="s">
+        <v>574</v>
+      </c>
+      <c r="E2357" s="11">
+        <v>3</v>
+      </c>
+      <c r="F2357">
+        <v>67</v>
+      </c>
+      <c r="G2357" t="s">
+        <v>575</v>
+      </c>
+    </row>
+    <row r="2358" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A2358" s="12" t="s">
+        <v>783</v>
+      </c>
+      <c r="B2358" s="10" t="s">
+        <v>301</v>
+      </c>
+      <c r="C2358" s="10" t="s">
+        <v>290</v>
+      </c>
+      <c r="D2358" s="4" t="s">
+        <v>574</v>
+      </c>
+      <c r="E2358" s="11">
+        <v>3</v>
+      </c>
+      <c r="F2358">
+        <v>55</v>
+      </c>
+      <c r="G2358" t="s">
+        <v>579</v>
+      </c>
+    </row>
+    <row r="2359" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A2359" s="12" t="s">
+        <v>784</v>
+      </c>
+      <c r="B2359" s="10" t="s">
+        <v>303</v>
+      </c>
+      <c r="C2359" s="10" t="s">
+        <v>290</v>
+      </c>
+      <c r="D2359" s="4" t="s">
+        <v>574</v>
+      </c>
+      <c r="E2359" s="11">
+        <v>3</v>
+      </c>
+      <c r="F2359">
+        <v>98</v>
+      </c>
+      <c r="G2359" t="s">
+        <v>593</v>
+      </c>
+    </row>
+    <row r="2360" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A2360" s="12" t="s">
+        <v>785</v>
+      </c>
+      <c r="B2360" s="10" t="s">
+        <v>305</v>
+      </c>
+      <c r="C2360" s="10" t="s">
+        <v>290</v>
+      </c>
+      <c r="D2360" s="4" t="s">
+        <v>574</v>
+      </c>
+      <c r="E2360" s="11">
+        <v>3</v>
+      </c>
+      <c r="F2360">
+        <v>69</v>
+      </c>
+      <c r="G2360" t="s">
+        <v>575</v>
+      </c>
+    </row>
+    <row r="2361" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A2361" s="12" t="s">
+        <v>786</v>
+      </c>
+      <c r="B2361" s="10" t="s">
+        <v>308</v>
+      </c>
+      <c r="C2361" s="10" t="s">
+        <v>290</v>
+      </c>
+      <c r="D2361" s="4" t="s">
+        <v>574</v>
+      </c>
+      <c r="E2361" s="11">
+        <v>3</v>
+      </c>
+      <c r="F2361">
+        <v>65</v>
+      </c>
+      <c r="G2361" t="s">
+        <v>575</v>
+      </c>
+    </row>
+    <row r="2362" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A2362" s="12" t="s">
+        <v>787</v>
+      </c>
+      <c r="B2362" s="10" t="s">
+        <v>309</v>
+      </c>
+      <c r="C2362" s="10" t="s">
+        <v>290</v>
+      </c>
+      <c r="D2362" s="4" t="s">
+        <v>574</v>
+      </c>
+      <c r="E2362" s="11">
+        <v>3</v>
+      </c>
+      <c r="F2362">
+        <v>65</v>
+      </c>
+      <c r="G2362" t="s">
+        <v>575</v>
+      </c>
+    </row>
+    <row r="2363" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A2363" s="12" t="s">
+        <v>788</v>
+      </c>
+      <c r="B2363" s="10" t="s">
+        <v>311</v>
+      </c>
+      <c r="C2363" s="10" t="s">
+        <v>290</v>
+      </c>
+      <c r="D2363" s="4" t="s">
+        <v>574</v>
+      </c>
+      <c r="E2363" s="11">
+        <v>3</v>
+      </c>
+      <c r="F2363">
+        <v>70</v>
+      </c>
+      <c r="G2363" t="s">
+        <v>575</v>
+      </c>
+    </row>
+    <row r="2364" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A2364" s="12" t="s">
+        <v>789</v>
+      </c>
+      <c r="B2364" s="10" t="s">
+        <v>315</v>
+      </c>
+      <c r="C2364" s="10" t="s">
+        <v>290</v>
+      </c>
+      <c r="D2364" s="4" t="s">
+        <v>574</v>
+      </c>
+      <c r="E2364" s="11">
+        <v>3</v>
+      </c>
+      <c r="F2364">
+        <v>55</v>
+      </c>
+      <c r="G2364" t="s">
+        <v>579</v>
+      </c>
+    </row>
+    <row r="2365" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A2365" s="12" t="s">
+        <v>790</v>
+      </c>
+      <c r="B2365" s="10" t="s">
+        <v>316</v>
+      </c>
+      <c r="C2365" s="10" t="s">
+        <v>290</v>
+      </c>
+      <c r="D2365" s="4" t="s">
+        <v>574</v>
+      </c>
+      <c r="E2365" s="11">
+        <v>3</v>
+      </c>
+      <c r="F2365">
+        <v>55</v>
+      </c>
+      <c r="G2365" t="s">
+        <v>579</v>
+      </c>
+    </row>
+    <row r="2366" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A2366" s="12" t="s">
+        <v>791</v>
+      </c>
+      <c r="B2366" s="10" t="s">
+        <v>317</v>
+      </c>
+      <c r="C2366" s="10" t="s">
+        <v>290</v>
+      </c>
+      <c r="D2366" s="4" t="s">
+        <v>574</v>
+      </c>
+      <c r="E2366" s="11">
+        <v>3</v>
+      </c>
+      <c r="F2366">
+        <v>70</v>
+      </c>
+      <c r="G2366" t="s">
+        <v>575</v>
+      </c>
+    </row>
+    <row r="2367" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A2367" s="12" t="s">
+        <v>792</v>
+      </c>
+      <c r="B2367" s="10" t="s">
+        <v>418</v>
+      </c>
+      <c r="C2367" s="10" t="s">
+        <v>290</v>
+      </c>
+      <c r="D2367" s="4" t="s">
+        <v>574</v>
+      </c>
+      <c r="E2367" s="11">
+        <v>3</v>
+      </c>
+      <c r="F2367">
+        <v>77</v>
+      </c>
+      <c r="G2367" t="s">
+        <v>575</v>
+      </c>
+    </row>
+    <row r="2368" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A2368" s="12" t="s">
+        <v>793</v>
+      </c>
+      <c r="B2368" s="10" t="s">
+        <v>320</v>
+      </c>
+      <c r="C2368" s="10" t="s">
+        <v>290</v>
+      </c>
+      <c r="D2368" s="4" t="s">
+        <v>574</v>
+      </c>
+      <c r="E2368" s="11">
+        <v>3</v>
+      </c>
+      <c r="F2368">
+        <v>70</v>
+      </c>
+      <c r="G2368" t="s">
+        <v>575</v>
+      </c>
+    </row>
+    <row r="2369" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A2369" s="12" t="s">
+        <v>794</v>
+      </c>
+      <c r="B2369" s="10" t="s">
+        <v>321</v>
+      </c>
+      <c r="C2369" s="10" t="s">
+        <v>290</v>
+      </c>
+      <c r="D2369" s="4" t="s">
+        <v>574</v>
+      </c>
+      <c r="E2369" s="11">
+        <v>3</v>
+      </c>
+      <c r="F2369">
+        <v>78</v>
+      </c>
+      <c r="G2369" t="s">
+        <v>575</v>
+      </c>
+    </row>
+    <row r="2370" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A2370" s="12" t="s">
+        <v>795</v>
+      </c>
+      <c r="B2370" s="10" t="s">
+        <v>322</v>
+      </c>
+      <c r="C2370" s="10" t="s">
+        <v>290</v>
+      </c>
+      <c r="D2370" s="4" t="s">
+        <v>574</v>
+      </c>
+      <c r="E2370" s="11">
+        <v>3</v>
+      </c>
+      <c r="F2370">
+        <v>55</v>
+      </c>
+      <c r="G2370" t="s">
+        <v>579</v>
+      </c>
+    </row>
+    <row r="2371" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A2371" s="12" t="s">
+        <v>796</v>
+      </c>
+      <c r="B2371" s="10" t="s">
+        <v>416</v>
+      </c>
+      <c r="C2371" s="10" t="s">
+        <v>290</v>
+      </c>
+      <c r="D2371" s="4" t="s">
+        <v>574</v>
+      </c>
+      <c r="E2371" s="11">
+        <v>3</v>
+      </c>
+      <c r="F2371">
+        <v>70</v>
+      </c>
+      <c r="G2371" t="s">
+        <v>575</v>
+      </c>
+    </row>
+    <row r="2372" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A2372" s="12" t="s">
+        <v>797</v>
+      </c>
+      <c r="B2372" s="10" t="s">
+        <v>323</v>
+      </c>
+      <c r="C2372" s="10" t="s">
+        <v>290</v>
+      </c>
+      <c r="D2372" s="4" t="s">
+        <v>574</v>
+      </c>
+      <c r="E2372" s="11">
+        <v>3</v>
+      </c>
+      <c r="F2372">
+        <v>70</v>
+      </c>
+      <c r="G2372" t="s">
+        <v>575</v>
+      </c>
+    </row>
+    <row r="2373" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A2373" s="12" t="s">
+        <v>798</v>
+      </c>
+      <c r="B2373" s="10" t="s">
+        <v>325</v>
+      </c>
+      <c r="C2373" s="10" t="s">
+        <v>290</v>
+      </c>
+      <c r="D2373" s="4" t="s">
+        <v>574</v>
+      </c>
+      <c r="E2373" s="11">
+        <v>3</v>
+      </c>
+      <c r="F2373">
+        <v>82</v>
+      </c>
+      <c r="G2373" t="s">
+        <v>577</v>
+      </c>
+    </row>
+    <row r="2374" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A2374" s="12" t="s">
+        <v>799</v>
+      </c>
+      <c r="B2374" s="10" t="s">
+        <v>327</v>
+      </c>
+      <c r="C2374" s="10" t="s">
+        <v>290</v>
+      </c>
+      <c r="D2374" s="4" t="s">
+        <v>574</v>
+      </c>
+      <c r="E2374" s="11">
+        <v>3</v>
+      </c>
+      <c r="F2374">
+        <v>70</v>
+      </c>
+      <c r="G2374" t="s">
+        <v>575</v>
+      </c>
+    </row>
+    <row r="2375" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A2375" s="12" t="s">
+        <v>800</v>
+      </c>
+      <c r="B2375" s="10" t="s">
+        <v>329</v>
+      </c>
+      <c r="C2375" s="10" t="s">
+        <v>290</v>
+      </c>
+      <c r="D2375" s="4" t="s">
+        <v>574</v>
+      </c>
+      <c r="E2375" s="11">
+        <v>3</v>
+      </c>
+      <c r="F2375">
+        <v>70</v>
+      </c>
+      <c r="G2375" t="s">
+        <v>575</v>
+      </c>
+    </row>
+    <row r="2376" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A2376" s="12" t="s">
+        <v>801</v>
+      </c>
+      <c r="B2376" s="10" t="s">
+        <v>330</v>
+      </c>
+      <c r="C2376" s="10" t="s">
+        <v>290</v>
+      </c>
+      <c r="D2376" s="4" t="s">
+        <v>574</v>
+      </c>
+      <c r="E2376" s="11">
+        <v>3</v>
+      </c>
+      <c r="F2376">
+        <v>68</v>
+      </c>
+      <c r="G2376" t="s">
+        <v>575</v>
+      </c>
+    </row>
+    <row r="2377" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A2377" s="12" t="s">
+        <v>802</v>
+      </c>
+      <c r="B2377" s="10" t="s">
+        <v>331</v>
+      </c>
+      <c r="C2377" s="10" t="s">
+        <v>290</v>
+      </c>
+      <c r="D2377" s="4" t="s">
+        <v>574</v>
+      </c>
+      <c r="E2377" s="11">
+        <v>3</v>
+      </c>
+      <c r="F2377">
+        <v>98</v>
+      </c>
+      <c r="G2377" t="s">
+        <v>593</v>
+      </c>
+    </row>
+    <row r="2378" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A2378" s="12" t="s">
+        <v>803</v>
+      </c>
+      <c r="B2378" s="10" t="s">
+        <v>332</v>
+      </c>
+      <c r="C2378" s="10" t="s">
+        <v>290</v>
+      </c>
+      <c r="D2378" s="4" t="s">
+        <v>574</v>
+      </c>
+      <c r="E2378" s="11">
+        <v>3</v>
+      </c>
+      <c r="F2378">
+        <v>100</v>
+      </c>
+      <c r="G2378" t="s">
+        <v>593</v>
+      </c>
+    </row>
+    <row r="2379" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A2379" s="12" t="s">
+        <v>804</v>
+      </c>
+      <c r="B2379" s="10" t="s">
+        <v>333</v>
+      </c>
+      <c r="C2379" s="10" t="s">
+        <v>290</v>
+      </c>
+      <c r="D2379" s="4" t="s">
+        <v>574</v>
+      </c>
+      <c r="E2379" s="11">
+        <v>3</v>
+      </c>
+      <c r="F2379">
+        <v>69</v>
+      </c>
+      <c r="G2379" t="s">
+        <v>575</v>
+      </c>
+    </row>
+    <row r="2380" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A2380" s="12" t="s">
+        <v>805</v>
+      </c>
+      <c r="B2380" s="10" t="s">
+        <v>334</v>
+      </c>
+      <c r="C2380" s="10" t="s">
+        <v>290</v>
+      </c>
+      <c r="D2380" s="4" t="s">
+        <v>574</v>
+      </c>
+      <c r="E2380" s="11">
+        <v>3</v>
+      </c>
+      <c r="F2380">
+        <v>65</v>
+      </c>
+      <c r="G2380" t="s">
+        <v>575</v>
+      </c>
+    </row>
+    <row r="2381" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A2381" s="12" t="s">
+        <v>806</v>
+      </c>
+      <c r="B2381" s="10" t="s">
+        <v>335</v>
+      </c>
+      <c r="C2381" s="10" t="s">
+        <v>290</v>
+      </c>
+      <c r="D2381" s="4" t="s">
+        <v>574</v>
+      </c>
+      <c r="E2381" s="11">
+        <v>3</v>
+      </c>
+      <c r="F2381">
+        <v>70</v>
+      </c>
+      <c r="G2381" t="s">
+        <v>575</v>
+      </c>
+    </row>
+    <row r="2382" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A2382" s="12" t="s">
+        <v>807</v>
+      </c>
+      <c r="B2382" s="10" t="s">
+        <v>336</v>
+      </c>
+      <c r="C2382" s="10" t="s">
+        <v>290</v>
+      </c>
+      <c r="D2382" s="4" t="s">
+        <v>574</v>
+      </c>
+      <c r="E2382" s="11">
+        <v>3</v>
+      </c>
+      <c r="F2382">
+        <v>65</v>
+      </c>
+      <c r="G2382" t="s">
+        <v>575</v>
+      </c>
+    </row>
+    <row r="2383" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A2383" s="12" t="s">
+        <v>808</v>
+      </c>
+      <c r="B2383" s="10" t="s">
+        <v>339</v>
+      </c>
+      <c r="C2383" s="10" t="s">
+        <v>290</v>
+      </c>
+      <c r="D2383" s="4" t="s">
+        <v>574</v>
+      </c>
+      <c r="E2383" s="11">
+        <v>3</v>
+      </c>
+      <c r="F2383">
+        <v>96</v>
+      </c>
+      <c r="G2383" t="s">
+        <v>593</v>
+      </c>
+    </row>
+    <row r="2384" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A2384" s="12" t="s">
+        <v>809</v>
+      </c>
+      <c r="B2384" s="10" t="s">
+        <v>342</v>
+      </c>
+      <c r="C2384" s="10" t="s">
+        <v>290</v>
+      </c>
+      <c r="D2384" s="4" t="s">
+        <v>574</v>
+      </c>
+      <c r="E2384" s="11">
+        <v>3</v>
+      </c>
+      <c r="F2384">
+        <v>55</v>
+      </c>
+      <c r="G2384" t="s">
+        <v>579</v>
+      </c>
+    </row>
+    <row r="2385" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A2385" s="12" t="s">
+        <v>810</v>
+      </c>
+      <c r="B2385" s="10" t="s">
+        <v>343</v>
+      </c>
+      <c r="C2385" s="10" t="s">
+        <v>290</v>
+      </c>
+      <c r="D2385" s="4" t="s">
+        <v>574</v>
+      </c>
+      <c r="E2385" s="11">
+        <v>3</v>
+      </c>
+      <c r="F2385">
+        <v>55</v>
+      </c>
+      <c r="G2385" t="s">
+        <v>579</v>
+      </c>
+    </row>
+    <row r="2386" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A2386" s="12" t="s">
+        <v>811</v>
+      </c>
+      <c r="B2386" s="10" t="s">
+        <v>344</v>
+      </c>
+      <c r="C2386" s="10" t="s">
+        <v>290</v>
+      </c>
+      <c r="D2386" s="4" t="s">
+        <v>574</v>
+      </c>
+      <c r="E2386" s="11">
+        <v>3</v>
+      </c>
+      <c r="F2386">
+        <v>98</v>
+      </c>
+      <c r="G2386" t="s">
+        <v>593</v>
+      </c>
+    </row>
+    <row r="2387" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A2387" s="12" t="s">
+        <v>812</v>
+      </c>
+      <c r="B2387" s="10" t="s">
+        <v>345</v>
+      </c>
+      <c r="C2387" s="10" t="s">
+        <v>290</v>
+      </c>
+      <c r="D2387" s="4" t="s">
+        <v>574</v>
+      </c>
+      <c r="E2387" s="11">
+        <v>3</v>
+      </c>
+      <c r="F2387">
+        <v>78</v>
+      </c>
+      <c r="G2387" t="s">
+        <v>575</v>
+      </c>
+    </row>
+    <row r="2388" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A2388" s="12" t="s">
+        <v>813</v>
+      </c>
+      <c r="B2388" s="10" t="s">
+        <v>346</v>
+      </c>
+      <c r="C2388" s="10" t="s">
+        <v>290</v>
+      </c>
+      <c r="D2388" s="4" t="s">
+        <v>574</v>
+      </c>
+      <c r="E2388" s="11">
+        <v>3</v>
+      </c>
+      <c r="F2388">
+        <v>70</v>
+      </c>
+      <c r="G2388" t="s">
+        <v>575</v>
+      </c>
+    </row>
+    <row r="2389" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A2389" s="12" t="s">
+        <v>814</v>
+      </c>
+      <c r="B2389" s="10" t="s">
+        <v>417</v>
+      </c>
+      <c r="C2389" s="10" t="s">
+        <v>290</v>
+      </c>
+      <c r="D2389" s="4" t="s">
+        <v>574</v>
+      </c>
+      <c r="E2389" s="11">
+        <v>3</v>
+      </c>
+      <c r="F2389">
+        <v>87</v>
+      </c>
+      <c r="G2389" t="s">
+        <v>577</v>
+      </c>
+    </row>
+    <row r="2390" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A2390" s="12" t="s">
+        <v>815</v>
+      </c>
+      <c r="B2390" s="10" t="s">
+        <v>347</v>
+      </c>
+      <c r="C2390" s="10" t="s">
+        <v>290</v>
+      </c>
+      <c r="D2390" s="4" t="s">
+        <v>574</v>
+      </c>
+      <c r="E2390" s="11">
+        <v>3</v>
+      </c>
+      <c r="F2390">
+        <v>70</v>
+      </c>
+      <c r="G2390" t="s">
+        <v>575</v>
+      </c>
+    </row>
+    <row r="2391" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A2391" s="12" t="s">
+        <v>816</v>
+      </c>
+      <c r="B2391" s="10" t="s">
+        <v>351</v>
+      </c>
+      <c r="C2391" s="10" t="s">
+        <v>290</v>
+      </c>
+      <c r="D2391" s="4" t="s">
+        <v>574</v>
+      </c>
+      <c r="E2391" s="11">
+        <v>3</v>
+      </c>
+      <c r="F2391">
+        <v>68</v>
+      </c>
+      <c r="G2391" t="s">
+        <v>575</v>
+      </c>
+    </row>
+    <row r="2392" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A2392" s="12" t="s">
+        <v>817</v>
+      </c>
+      <c r="B2392" s="10" t="s">
+        <v>352</v>
+      </c>
+      <c r="C2392" s="10" t="s">
+        <v>290</v>
+      </c>
+      <c r="D2392" s="4" t="s">
+        <v>574</v>
+      </c>
+      <c r="E2392" s="11">
+        <v>3</v>
+      </c>
+      <c r="F2392">
+        <v>69</v>
+      </c>
+      <c r="G2392" t="s">
+        <v>575</v>
+      </c>
+    </row>
+    <row r="2393" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A2393" s="12" t="s">
+        <v>818</v>
+      </c>
+      <c r="B2393" s="10" t="s">
+        <v>446</v>
+      </c>
+      <c r="C2393" s="10" t="s">
+        <v>570</v>
+      </c>
+      <c r="D2393" s="4" t="s">
+        <v>574</v>
+      </c>
+      <c r="E2393" s="11">
+        <v>3</v>
+      </c>
+      <c r="F2393">
+        <v>55</v>
+      </c>
+      <c r="G2393" t="s">
+        <v>579</v>
+      </c>
+    </row>
+    <row r="2394" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A2394" s="12" t="s">
+        <v>819</v>
+      </c>
+      <c r="B2394" s="10" t="s">
+        <v>447</v>
+      </c>
+      <c r="C2394" s="10" t="s">
+        <v>570</v>
+      </c>
+      <c r="D2394" s="4" t="s">
+        <v>574</v>
+      </c>
+      <c r="E2394" s="11">
+        <v>3</v>
+      </c>
+      <c r="F2394">
+        <v>67</v>
+      </c>
+      <c r="G2394" t="s">
+        <v>575</v>
+      </c>
+    </row>
+    <row r="2395" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A2395" s="12" t="s">
+        <v>820</v>
+      </c>
+      <c r="B2395" s="10" t="s">
+        <v>448</v>
+      </c>
+      <c r="C2395" s="10" t="s">
+        <v>570</v>
+      </c>
+      <c r="D2395" s="4" t="s">
+        <v>574</v>
+      </c>
+      <c r="E2395" s="11">
+        <v>3</v>
+      </c>
+      <c r="F2395">
+        <v>80</v>
+      </c>
+      <c r="G2395" t="s">
+        <v>577</v>
+      </c>
+    </row>
+    <row r="2396" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A2396" s="12" t="s">
+        <v>821</v>
+      </c>
+      <c r="B2396" s="10" t="s">
+        <v>449</v>
+      </c>
+      <c r="C2396" s="10" t="s">
+        <v>570</v>
+      </c>
+      <c r="D2396" s="4" t="s">
+        <v>574</v>
+      </c>
+      <c r="E2396" s="11">
+        <v>3</v>
+      </c>
+      <c r="F2396">
+        <v>75</v>
+      </c>
+      <c r="G2396" t="s">
+        <v>575</v>
+      </c>
+    </row>
+    <row r="2397" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A2397" s="12" t="s">
+        <v>822</v>
+      </c>
+      <c r="B2397" s="10" t="s">
+        <v>450</v>
+      </c>
+      <c r="C2397" s="10" t="s">
+        <v>570</v>
+      </c>
+      <c r="D2397" s="4" t="s">
+        <v>574</v>
+      </c>
+      <c r="E2397" s="11">
+        <v>3</v>
+      </c>
+      <c r="F2397">
+        <v>55</v>
+      </c>
+      <c r="G2397" t="s">
+        <v>579</v>
+      </c>
+    </row>
+    <row r="2398" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A2398" s="12" t="s">
+        <v>823</v>
+      </c>
+      <c r="B2398" s="10" t="s">
+        <v>451</v>
+      </c>
+      <c r="C2398" s="10" t="s">
+        <v>570</v>
+      </c>
+      <c r="D2398" s="4" t="s">
+        <v>574</v>
+      </c>
+      <c r="E2398" s="11">
+        <v>3</v>
+      </c>
+      <c r="F2398">
+        <v>75</v>
+      </c>
+      <c r="G2398" t="s">
+        <v>575</v>
+      </c>
+    </row>
+    <row r="2399" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A2399" s="12" t="s">
+        <v>824</v>
+      </c>
+      <c r="B2399" s="10" t="s">
+        <v>452</v>
+      </c>
+      <c r="C2399" s="10" t="s">
+        <v>570</v>
+      </c>
+      <c r="D2399" s="4" t="s">
+        <v>574</v>
+      </c>
+      <c r="E2399" s="11">
+        <v>3</v>
+      </c>
+      <c r="F2399">
+        <v>69</v>
+      </c>
+      <c r="G2399" t="s">
+        <v>575</v>
+      </c>
+    </row>
+    <row r="2400" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A2400" s="12" t="s">
+        <v>825</v>
+      </c>
+      <c r="B2400" s="10" t="s">
+        <v>453</v>
+      </c>
+      <c r="C2400" s="10" t="s">
+        <v>570</v>
+      </c>
+      <c r="D2400" s="4" t="s">
+        <v>574</v>
+      </c>
+      <c r="E2400" s="11">
+        <v>3</v>
+      </c>
+      <c r="F2400">
+        <v>69</v>
+      </c>
+      <c r="G2400" t="s">
+        <v>575</v>
+      </c>
+    </row>
+    <row r="2401" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A2401" s="12" t="s">
+        <v>826</v>
+      </c>
+      <c r="B2401" s="10" t="s">
+        <v>454</v>
+      </c>
+      <c r="C2401" s="10" t="s">
+        <v>570</v>
+      </c>
+      <c r="D2401" s="4" t="s">
+        <v>574</v>
+      </c>
+      <c r="E2401" s="11">
+        <v>3</v>
+      </c>
+      <c r="F2401">
+        <v>70</v>
+      </c>
+      <c r="G2401" t="s">
+        <v>575</v>
+      </c>
+    </row>
+    <row r="2402" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A2402" s="12" t="s">
+        <v>827</v>
+      </c>
+      <c r="B2402" s="10" t="s">
+        <v>455</v>
+      </c>
+      <c r="C2402" s="10" t="s">
+        <v>570</v>
+      </c>
+      <c r="D2402" s="4" t="s">
+        <v>574</v>
+      </c>
+      <c r="E2402" s="11">
+        <v>3</v>
+      </c>
+      <c r="F2402">
+        <v>92</v>
+      </c>
+      <c r="G2402" t="s">
+        <v>593</v>
+      </c>
+    </row>
+    <row r="2403" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A2403" s="12" t="s">
+        <v>828</v>
+      </c>
+      <c r="B2403" s="10" t="s">
+        <v>456</v>
+      </c>
+      <c r="C2403" s="10" t="s">
+        <v>570</v>
+      </c>
+      <c r="D2403" s="4" t="s">
+        <v>574</v>
+      </c>
+      <c r="E2403" s="11">
+        <v>3</v>
+      </c>
+      <c r="F2403">
+        <v>100</v>
+      </c>
+      <c r="G2403" t="s">
+        <v>593</v>
+      </c>
+    </row>
+    <row r="2404" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A2404" s="12" t="s">
+        <v>829</v>
+      </c>
+      <c r="B2404" s="10" t="s">
+        <v>236</v>
+      </c>
+      <c r="C2404" s="10" t="s">
+        <v>570</v>
+      </c>
+      <c r="D2404" s="4" t="s">
+        <v>574</v>
+      </c>
+      <c r="E2404" s="11">
+        <v>3</v>
+      </c>
+      <c r="F2404">
+        <v>91</v>
+      </c>
+      <c r="G2404" t="s">
+        <v>593</v>
+      </c>
+    </row>
+    <row r="2405" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A2405" s="12" t="s">
+        <v>830</v>
+      </c>
+      <c r="B2405" s="10" t="s">
+        <v>430</v>
+      </c>
+      <c r="C2405" s="10" t="s">
+        <v>570</v>
+      </c>
+      <c r="D2405" s="4" t="s">
+        <v>574</v>
+      </c>
+      <c r="E2405" s="11">
+        <v>3</v>
+      </c>
+      <c r="F2405">
+        <v>69</v>
+      </c>
+      <c r="G2405" t="s">
+        <v>575</v>
+      </c>
+    </row>
+    <row r="2406" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A2406" s="12" t="s">
+        <v>831</v>
+      </c>
+      <c r="B2406" s="10" t="s">
+        <v>457</v>
+      </c>
+      <c r="C2406" s="10" t="s">
+        <v>570</v>
+      </c>
+      <c r="D2406" s="4" t="s">
+        <v>574</v>
+      </c>
+      <c r="E2406" s="11">
+        <v>3</v>
+      </c>
+      <c r="F2406">
+        <v>69</v>
+      </c>
+      <c r="G2406" t="s">
+        <v>575</v>
+      </c>
+    </row>
+    <row r="2407" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A2407" s="12" t="s">
+        <v>832</v>
+      </c>
+      <c r="B2407" s="10" t="s">
+        <v>458</v>
+      </c>
+      <c r="C2407" s="10" t="s">
+        <v>570</v>
+      </c>
+      <c r="D2407" s="4" t="s">
+        <v>574</v>
+      </c>
+      <c r="E2407" s="11">
+        <v>3</v>
+      </c>
+      <c r="F2407">
+        <v>55</v>
+      </c>
+      <c r="G2407" t="s">
+        <v>579</v>
+      </c>
+    </row>
+    <row r="2408" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A2408" s="12" t="s">
+        <v>833</v>
+      </c>
+      <c r="B2408" s="10" t="s">
+        <v>459</v>
+      </c>
+      <c r="C2408" s="10" t="s">
+        <v>570</v>
+      </c>
+      <c r="D2408" s="4" t="s">
+        <v>574</v>
+      </c>
+      <c r="E2408" s="11">
+        <v>3</v>
+      </c>
+      <c r="F2408">
+        <v>67</v>
+      </c>
+      <c r="G2408" t="s">
+        <v>575</v>
+      </c>
+    </row>
+    <row r="2409" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A2409" s="12" t="s">
+        <v>834</v>
+      </c>
+      <c r="B2409" s="10" t="s">
+        <v>461</v>
+      </c>
+      <c r="C2409" s="10" t="s">
+        <v>570</v>
+      </c>
+      <c r="D2409" s="4" t="s">
+        <v>574</v>
+      </c>
+      <c r="E2409" s="11">
+        <v>3</v>
+      </c>
+      <c r="F2409">
+        <v>84</v>
+      </c>
+      <c r="G2409" t="s">
+        <v>577</v>
+      </c>
+    </row>
+    <row r="2410" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A2410" s="12" t="s">
+        <v>835</v>
+      </c>
+      <c r="B2410" s="10" t="s">
+        <v>462</v>
+      </c>
+      <c r="C2410" s="10" t="s">
+        <v>570</v>
+      </c>
+      <c r="D2410" s="4" t="s">
+        <v>574</v>
+      </c>
+      <c r="E2410" s="11">
+        <v>3</v>
+      </c>
+      <c r="F2410">
+        <v>76</v>
+      </c>
+      <c r="G2410" t="s">
+        <v>575</v>
+      </c>
+    </row>
+    <row r="2411" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A2411" s="12" t="s">
+        <v>836</v>
+      </c>
+      <c r="B2411" s="10" t="s">
+        <v>463</v>
+      </c>
+      <c r="C2411" s="10" t="s">
+        <v>570</v>
+      </c>
+      <c r="D2411" s="4" t="s">
+        <v>574</v>
+      </c>
+      <c r="E2411" s="11">
+        <v>3</v>
+      </c>
+      <c r="F2411">
+        <v>75</v>
+      </c>
+      <c r="G2411" t="s">
+        <v>575</v>
+      </c>
+    </row>
+    <row r="2412" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A2412" s="12" t="s">
+        <v>837</v>
+      </c>
+      <c r="B2412" s="10" t="s">
+        <v>464</v>
+      </c>
+      <c r="C2412" s="10" t="s">
+        <v>570</v>
+      </c>
+      <c r="D2412" s="4" t="s">
+        <v>574</v>
+      </c>
+      <c r="E2412" s="11">
+        <v>3</v>
+      </c>
+      <c r="F2412">
+        <v>67</v>
+      </c>
+      <c r="G2412" t="s">
+        <v>575</v>
+      </c>
+    </row>
+    <row r="2413" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A2413" s="12" t="s">
+        <v>838</v>
+      </c>
+      <c r="B2413" s="10" t="s">
+        <v>444</v>
+      </c>
+      <c r="C2413" s="10" t="s">
+        <v>570</v>
+      </c>
+      <c r="D2413" s="4" t="s">
+        <v>574</v>
+      </c>
+      <c r="E2413" s="11">
+        <v>3</v>
+      </c>
+      <c r="F2413">
+        <v>67</v>
+      </c>
+      <c r="G2413" t="s">
+        <v>575</v>
+      </c>
+    </row>
+    <row r="2414" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A2414" s="12" t="s">
+        <v>839</v>
+      </c>
+      <c r="B2414" s="10" t="s">
+        <v>465</v>
+      </c>
+      <c r="C2414" s="10" t="s">
+        <v>570</v>
+      </c>
+      <c r="D2414" s="4" t="s">
+        <v>574</v>
+      </c>
+      <c r="E2414" s="11">
+        <v>3</v>
+      </c>
+      <c r="F2414">
+        <v>67</v>
+      </c>
+      <c r="G2414" t="s">
+        <v>575</v>
+      </c>
+    </row>
+    <row r="2415" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A2415" s="12" t="s">
+        <v>840</v>
+      </c>
+      <c r="B2415" s="10" t="s">
+        <v>420</v>
+      </c>
+      <c r="C2415" s="10" t="s">
+        <v>570</v>
+      </c>
+      <c r="D2415" s="4" t="s">
+        <v>574</v>
+      </c>
+      <c r="E2415" s="11">
+        <v>3</v>
+      </c>
+      <c r="F2415">
+        <v>70</v>
+      </c>
+      <c r="G2415" t="s">
+        <v>575</v>
+      </c>
+    </row>
+    <row r="2416" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A2416" s="12" t="s">
+        <v>841</v>
+      </c>
+      <c r="B2416" s="10" t="s">
+        <v>429</v>
+      </c>
+      <c r="C2416" s="10" t="s">
+        <v>570</v>
+      </c>
+      <c r="D2416" s="4" t="s">
+        <v>574</v>
+      </c>
+      <c r="E2416" s="11">
+        <v>3</v>
+      </c>
+      <c r="F2416">
+        <v>84</v>
+      </c>
+      <c r="G2416" t="s">
+        <v>577</v>
+      </c>
+    </row>
+    <row r="2417" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A2417" s="12" t="s">
+        <v>842</v>
+      </c>
+      <c r="B2417" s="10" t="s">
+        <v>428</v>
+      </c>
+      <c r="C2417" s="10" t="s">
+        <v>570</v>
+      </c>
+      <c r="D2417" s="4" t="s">
+        <v>574</v>
+      </c>
+      <c r="E2417" s="11">
+        <v>3</v>
+      </c>
+      <c r="F2417">
+        <v>100</v>
+      </c>
+      <c r="G2417" t="s">
+        <v>593</v>
+      </c>
+    </row>
+    <row r="2418" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A2418" s="12" t="s">
+        <v>843</v>
+      </c>
+      <c r="B2418" s="10" t="s">
+        <v>427</v>
+      </c>
+      <c r="C2418" s="10" t="s">
+        <v>570</v>
+      </c>
+      <c r="D2418" s="4" t="s">
+        <v>574</v>
+      </c>
+      <c r="E2418" s="11">
+        <v>3</v>
+      </c>
+      <c r="F2418">
+        <v>98</v>
+      </c>
+      <c r="G2418" t="s">
+        <v>593</v>
+      </c>
+    </row>
+    <row r="2419" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A2419" s="12" t="s">
+        <v>844</v>
+      </c>
+      <c r="B2419" s="10" t="s">
+        <v>426</v>
+      </c>
+      <c r="C2419" s="10" t="s">
+        <v>570</v>
+      </c>
+      <c r="D2419" s="4" t="s">
+        <v>574</v>
+      </c>
+      <c r="E2419" s="11">
+        <v>3</v>
+      </c>
+      <c r="F2419">
+        <v>92</v>
+      </c>
+      <c r="G2419" t="s">
+        <v>593</v>
+      </c>
+    </row>
+    <row r="2420" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A2420" s="12" t="s">
+        <v>845</v>
+      </c>
+      <c r="B2420" s="10" t="s">
+        <v>425</v>
+      </c>
+      <c r="C2420" s="10" t="s">
+        <v>570</v>
+      </c>
+      <c r="D2420" s="4" t="s">
+        <v>574</v>
+      </c>
+      <c r="E2420" s="11">
+        <v>3</v>
+      </c>
+      <c r="F2420">
+        <v>82</v>
+      </c>
+      <c r="G2420" t="s">
+        <v>577</v>
+      </c>
+    </row>
+    <row r="2421" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A2421" s="12" t="s">
+        <v>846</v>
+      </c>
+      <c r="B2421" s="10" t="s">
+        <v>424</v>
+      </c>
+      <c r="C2421" s="10" t="s">
+        <v>570</v>
+      </c>
+      <c r="D2421" s="4" t="s">
+        <v>574</v>
+      </c>
+      <c r="E2421" s="11">
+        <v>3</v>
+      </c>
+      <c r="F2421">
+        <v>80</v>
+      </c>
+      <c r="G2421" t="s">
+        <v>577</v>
+      </c>
+    </row>
+    <row r="2422" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A2422" s="12" t="s">
+        <v>847</v>
+      </c>
+      <c r="B2422" s="10" t="s">
+        <v>423</v>
+      </c>
+      <c r="C2422" s="10" t="s">
+        <v>570</v>
+      </c>
+      <c r="D2422" s="4" t="s">
+        <v>574</v>
+      </c>
+      <c r="E2422" s="11">
+        <v>3</v>
+      </c>
+      <c r="F2422">
+        <v>86</v>
+      </c>
+      <c r="G2422" t="s">
+        <v>577</v>
+      </c>
+    </row>
+    <row r="2423" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A2423" s="12" t="s">
+        <v>848</v>
+      </c>
+      <c r="B2423" s="10" t="s">
+        <v>422</v>
+      </c>
+      <c r="C2423" s="10" t="s">
+        <v>570</v>
+      </c>
+      <c r="D2423" s="4" t="s">
+        <v>574</v>
+      </c>
+      <c r="E2423" s="11">
+        <v>3</v>
+      </c>
+      <c r="F2423">
+        <v>70</v>
+      </c>
+      <c r="G2423" t="s">
+        <v>575</v>
+      </c>
+    </row>
+    <row r="2424" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A2424" s="12" t="s">
+        <v>849</v>
+      </c>
+      <c r="B2424" s="10" t="s">
+        <v>421</v>
+      </c>
+      <c r="C2424" s="10" t="s">
+        <v>570</v>
+      </c>
+      <c r="D2424" s="4" t="s">
+        <v>574</v>
+      </c>
+      <c r="E2424" s="11">
+        <v>3</v>
+      </c>
+      <c r="F2424">
+        <v>70</v>
+      </c>
+      <c r="G2424" t="s">
+        <v>575</v>
+      </c>
+    </row>
+    <row r="2425" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A2425" s="12" t="s">
+        <v>850</v>
+      </c>
+      <c r="B2425" s="10" t="s">
+        <v>419</v>
+      </c>
+      <c r="C2425" s="10" t="s">
+        <v>570</v>
+      </c>
+      <c r="D2425" s="4" t="s">
+        <v>574</v>
+      </c>
+      <c r="E2425" s="11">
+        <v>3</v>
+      </c>
+      <c r="F2425">
+        <v>83</v>
+      </c>
+      <c r="G2425" t="s">
+        <v>577</v>
+      </c>
+    </row>
+    <row r="2426" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A2426" s="12" t="s">
+        <v>851</v>
+      </c>
+      <c r="B2426" s="10" t="s">
+        <v>431</v>
+      </c>
+      <c r="C2426" s="10" t="s">
+        <v>570</v>
+      </c>
+      <c r="D2426" s="4" t="s">
+        <v>574</v>
+      </c>
+      <c r="E2426" s="11">
+        <v>3</v>
+      </c>
+      <c r="F2426">
+        <v>67</v>
+      </c>
+      <c r="G2426" t="s">
+        <v>575</v>
+      </c>
+    </row>
+    <row r="2427" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A2427" s="12" t="s">
+        <v>852</v>
+      </c>
+      <c r="B2427" s="10" t="s">
+        <v>432</v>
+      </c>
+      <c r="C2427" s="10" t="s">
+        <v>570</v>
+      </c>
+      <c r="D2427" s="4" t="s">
+        <v>574</v>
+      </c>
+      <c r="E2427" s="11">
+        <v>3</v>
+      </c>
+      <c r="F2427">
+        <v>80</v>
+      </c>
+      <c r="G2427" t="s">
+        <v>577</v>
+      </c>
+    </row>
+    <row r="2428" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A2428" s="12" t="s">
+        <v>853</v>
+      </c>
+      <c r="B2428" s="10" t="s">
+        <v>435</v>
+      </c>
+      <c r="C2428" s="10" t="s">
+        <v>570</v>
+      </c>
+      <c r="D2428" s="4" t="s">
+        <v>574</v>
+      </c>
+      <c r="E2428" s="11">
+        <v>3</v>
+      </c>
+      <c r="F2428">
+        <v>84</v>
+      </c>
+      <c r="G2428" t="s">
+        <v>577</v>
+      </c>
+    </row>
+    <row r="2429" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A2429" s="12" t="s">
+        <v>854</v>
+      </c>
+      <c r="B2429" s="10" t="s">
+        <v>436</v>
+      </c>
+      <c r="C2429" s="10" t="s">
+        <v>570</v>
+      </c>
+      <c r="D2429" s="4" t="s">
+        <v>574</v>
+      </c>
+      <c r="E2429" s="11">
+        <v>3</v>
+      </c>
+      <c r="F2429">
+        <v>70</v>
+      </c>
+      <c r="G2429" t="s">
+        <v>575</v>
+      </c>
+    </row>
+    <row r="2430" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A2430" s="12" t="s">
+        <v>855</v>
+      </c>
+      <c r="B2430" s="10" t="s">
+        <v>437</v>
+      </c>
+      <c r="C2430" s="10" t="s">
+        <v>570</v>
+      </c>
+      <c r="D2430" s="4" t="s">
+        <v>574</v>
+      </c>
+      <c r="E2430" s="11">
+        <v>3</v>
+      </c>
+      <c r="F2430">
+        <v>55</v>
+      </c>
+      <c r="G2430" t="s">
+        <v>579</v>
+      </c>
+    </row>
+    <row r="2431" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A2431" s="12" t="s">
+        <v>856</v>
+      </c>
+      <c r="B2431" s="10" t="s">
+        <v>438</v>
+      </c>
+      <c r="C2431" s="10" t="s">
+        <v>570</v>
+      </c>
+      <c r="D2431" s="4" t="s">
+        <v>574</v>
+      </c>
+      <c r="E2431" s="11">
+        <v>3</v>
+      </c>
+      <c r="F2431">
+        <v>98</v>
+      </c>
+      <c r="G2431" t="s">
+        <v>593</v>
+      </c>
+    </row>
+    <row r="2432" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A2432" s="12" t="s">
+        <v>857</v>
+      </c>
+      <c r="B2432" s="10" t="s">
+        <v>439</v>
+      </c>
+      <c r="C2432" s="10" t="s">
+        <v>570</v>
+      </c>
+      <c r="D2432" s="4" t="s">
+        <v>574</v>
+      </c>
+      <c r="E2432" s="11">
+        <v>3</v>
+      </c>
+      <c r="F2432">
+        <v>70</v>
+      </c>
+      <c r="G2432" t="s">
+        <v>575</v>
+      </c>
+    </row>
+    <row r="2433" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A2433" s="12" t="s">
+        <v>858</v>
+      </c>
+      <c r="B2433" s="10" t="s">
+        <v>440</v>
+      </c>
+      <c r="C2433" s="10" t="s">
+        <v>570</v>
+      </c>
+      <c r="D2433" s="4" t="s">
+        <v>574</v>
+      </c>
+      <c r="E2433" s="11">
+        <v>3</v>
+      </c>
+      <c r="F2433">
+        <v>74</v>
+      </c>
+      <c r="G2433" t="s">
+        <v>575</v>
+      </c>
+    </row>
+    <row r="2434" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A2434" s="12" t="s">
+        <v>859</v>
+      </c>
+      <c r="B2434" s="10" t="s">
+        <v>566</v>
+      </c>
+      <c r="C2434" s="10" t="s">
+        <v>570</v>
+      </c>
+      <c r="D2434" s="4" t="s">
+        <v>574</v>
+      </c>
+      <c r="E2434" s="11">
+        <v>3</v>
+      </c>
+      <c r="F2434">
+        <v>74</v>
+      </c>
+      <c r="G2434" t="s">
+        <v>575</v>
+      </c>
+    </row>
+    <row r="2435" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A2435" s="12" t="s">
+        <v>860</v>
+      </c>
+      <c r="B2435" s="10" t="s">
+        <v>568</v>
+      </c>
+      <c r="C2435" s="10" t="s">
+        <v>570</v>
+      </c>
+      <c r="D2435" s="4" t="s">
+        <v>574</v>
+      </c>
+      <c r="E2435" s="11">
+        <v>3</v>
+      </c>
+      <c r="F2435">
+        <v>73</v>
+      </c>
+      <c r="G2435" t="s">
+        <v>575</v>
+      </c>
+    </row>
+    <row r="2436" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A2436" s="12" t="s">
+        <v>861</v>
+      </c>
+      <c r="B2436" s="10" t="s">
+        <v>467</v>
+      </c>
+      <c r="C2436" s="10" t="s">
+        <v>571</v>
+      </c>
+      <c r="D2436" s="4" t="s">
+        <v>574</v>
+      </c>
+      <c r="E2436" s="11">
+        <v>3</v>
+      </c>
+      <c r="F2436">
+        <v>70</v>
+      </c>
+      <c r="G2436" t="s">
+        <v>575</v>
+      </c>
+    </row>
+    <row r="2437" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A2437" s="12" t="s">
+        <v>862</v>
+      </c>
+      <c r="B2437" s="10" t="s">
+        <v>468</v>
+      </c>
+      <c r="C2437" s="10" t="s">
+        <v>571</v>
+      </c>
+      <c r="D2437" s="4" t="s">
+        <v>574</v>
+      </c>
+      <c r="E2437" s="11">
+        <v>3</v>
+      </c>
+      <c r="F2437">
+        <v>70</v>
+      </c>
+      <c r="G2437" t="s">
+        <v>575</v>
+      </c>
+    </row>
+    <row r="2438" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A2438" s="12" t="s">
+        <v>863</v>
+      </c>
+      <c r="B2438" s="10" t="s">
+        <v>480</v>
+      </c>
+      <c r="C2438" s="10" t="s">
+        <v>571</v>
+      </c>
+      <c r="D2438" s="4" t="s">
+        <v>574</v>
+      </c>
+      <c r="E2438" s="11">
+        <v>3</v>
+      </c>
+      <c r="F2438">
+        <v>55</v>
+      </c>
+      <c r="G2438" t="s">
+        <v>579</v>
+      </c>
+    </row>
+    <row r="2439" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A2439" s="12" t="s">
+        <v>864</v>
+      </c>
+      <c r="B2439" s="10" t="s">
+        <v>466</v>
+      </c>
+      <c r="C2439" s="10" t="s">
+        <v>571</v>
+      </c>
+      <c r="D2439" s="4" t="s">
+        <v>574</v>
+      </c>
+      <c r="E2439" s="11">
+        <v>3</v>
+      </c>
+      <c r="F2439">
+        <v>70</v>
+      </c>
+      <c r="G2439" t="s">
+        <v>575</v>
+      </c>
+    </row>
+    <row r="2440" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A2440" s="12" t="s">
+        <v>865</v>
+      </c>
+      <c r="B2440" s="10" t="s">
+        <v>493</v>
+      </c>
+      <c r="C2440" s="10" t="s">
+        <v>571</v>
+      </c>
+      <c r="D2440" s="4" t="s">
+        <v>574</v>
+      </c>
+      <c r="E2440" s="11">
+        <v>3</v>
+      </c>
+      <c r="F2440">
+        <v>73</v>
+      </c>
+      <c r="G2440" t="s">
+        <v>575</v>
+      </c>
+    </row>
+    <row r="2441" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A2441" s="12" t="s">
+        <v>866</v>
+      </c>
+      <c r="B2441" s="10" t="s">
+        <v>494</v>
+      </c>
+      <c r="C2441" s="10" t="s">
+        <v>571</v>
+      </c>
+      <c r="D2441" s="4" t="s">
+        <v>574</v>
+      </c>
+      <c r="E2441" s="11">
+        <v>3</v>
+      </c>
+      <c r="F2441">
+        <v>70</v>
+      </c>
+      <c r="G2441" t="s">
+        <v>575</v>
+      </c>
+    </row>
+    <row r="2442" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A2442" s="12" t="s">
+        <v>867</v>
+      </c>
+      <c r="B2442" s="10" t="s">
+        <v>496</v>
+      </c>
+      <c r="C2442" s="10" t="s">
+        <v>571</v>
+      </c>
+      <c r="D2442" s="4" t="s">
+        <v>574</v>
+      </c>
+      <c r="E2442" s="11">
+        <v>3</v>
+      </c>
+      <c r="F2442">
+        <v>70</v>
+      </c>
+      <c r="G2442" t="s">
+        <v>575</v>
+      </c>
+    </row>
+    <row r="2443" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A2443" s="12" t="s">
+        <v>868</v>
+      </c>
+      <c r="B2443" s="10" t="s">
+        <v>497</v>
+      </c>
+      <c r="C2443" s="10" t="s">
+        <v>571</v>
+      </c>
+      <c r="D2443" s="4" t="s">
+        <v>574</v>
+      </c>
+      <c r="E2443" s="11">
+        <v>3</v>
+      </c>
+      <c r="F2443">
+        <v>70</v>
+      </c>
+      <c r="G2443" t="s">
+        <v>575</v>
+      </c>
+    </row>
+    <row r="2444" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A2444" s="12" t="s">
+        <v>869</v>
+      </c>
+      <c r="B2444" s="10" t="s">
+        <v>498</v>
+      </c>
+      <c r="C2444" s="10" t="s">
+        <v>571</v>
+      </c>
+      <c r="D2444" s="4" t="s">
+        <v>574</v>
+      </c>
+      <c r="E2444" s="11">
+        <v>3</v>
+      </c>
+      <c r="F2444">
+        <v>74</v>
+      </c>
+      <c r="G2444" t="s">
+        <v>575</v>
+      </c>
+    </row>
+    <row r="2445" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A2445" s="12" t="s">
+        <v>870</v>
+      </c>
+      <c r="B2445" s="10" t="s">
+        <v>499</v>
+      </c>
+      <c r="C2445" s="10" t="s">
+        <v>571</v>
+      </c>
+      <c r="D2445" s="4" t="s">
+        <v>574</v>
+      </c>
+      <c r="E2445" s="11">
+        <v>3</v>
+      </c>
+      <c r="F2445">
+        <v>72</v>
+      </c>
+      <c r="G2445" t="s">
+        <v>575</v>
+      </c>
+    </row>
+    <row r="2446" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A2446" s="12" t="s">
+        <v>871</v>
+      </c>
+      <c r="B2446" s="10" t="s">
+        <v>500</v>
+      </c>
+      <c r="C2446" s="10" t="s">
+        <v>571</v>
+      </c>
+      <c r="D2446" s="4" t="s">
+        <v>574</v>
+      </c>
+      <c r="E2446" s="11">
+        <v>3</v>
+      </c>
+      <c r="F2446">
+        <v>72</v>
+      </c>
+      <c r="G2446" t="s">
+        <v>575</v>
+      </c>
+    </row>
+    <row r="2447" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A2447" s="12" t="s">
+        <v>872</v>
+      </c>
+      <c r="B2447" s="10" t="s">
+        <v>501</v>
+      </c>
+      <c r="C2447" s="10" t="s">
+        <v>571</v>
+      </c>
+      <c r="D2447" s="4" t="s">
+        <v>574</v>
+      </c>
+      <c r="E2447" s="11">
+        <v>3</v>
+      </c>
+      <c r="F2447">
+        <v>70</v>
+      </c>
+      <c r="G2447" t="s">
+        <v>575</v>
+      </c>
+    </row>
+    <row r="2448" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A2448" s="12" t="s">
+        <v>873</v>
+      </c>
+      <c r="B2448" s="10" t="s">
+        <v>502</v>
+      </c>
+      <c r="C2448" s="10" t="s">
+        <v>571</v>
+      </c>
+      <c r="D2448" s="4" t="s">
+        <v>574</v>
+      </c>
+      <c r="E2448" s="11">
+        <v>3</v>
+      </c>
+      <c r="F2448">
+        <v>55</v>
+      </c>
+      <c r="G2448" t="s">
+        <v>579</v>
+      </c>
+    </row>
+    <row r="2449" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A2449" s="12" t="s">
+        <v>874</v>
+      </c>
+      <c r="B2449" s="10" t="s">
+        <v>503</v>
+      </c>
+      <c r="C2449" s="10" t="s">
+        <v>571</v>
+      </c>
+      <c r="D2449" s="4" t="s">
+        <v>574</v>
+      </c>
+      <c r="E2449" s="11">
+        <v>3</v>
+      </c>
+      <c r="F2449">
+        <v>67</v>
+      </c>
+      <c r="G2449" t="s">
+        <v>575</v>
+      </c>
+    </row>
+    <row r="2450" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A2450" s="12" t="s">
+        <v>875</v>
+      </c>
+      <c r="B2450" s="10" t="s">
+        <v>504</v>
+      </c>
+      <c r="C2450" s="10" t="s">
+        <v>571</v>
+      </c>
+      <c r="D2450" s="4" t="s">
+        <v>574</v>
+      </c>
+      <c r="E2450" s="11">
+        <v>3</v>
+      </c>
+      <c r="F2450">
+        <v>74</v>
+      </c>
+      <c r="G2450" t="s">
+        <v>575</v>
+      </c>
+    </row>
+    <row r="2451" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A2451" s="12" t="s">
+        <v>876</v>
+      </c>
+      <c r="B2451" s="10" t="s">
+        <v>505</v>
+      </c>
+      <c r="C2451" s="10" t="s">
+        <v>571</v>
+      </c>
+      <c r="D2451" s="4" t="s">
+        <v>574</v>
+      </c>
+      <c r="E2451" s="11">
+        <v>3</v>
+      </c>
+      <c r="F2451">
+        <v>70</v>
+      </c>
+      <c r="G2451" t="s">
+        <v>575</v>
+      </c>
+    </row>
+    <row r="2452" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A2452" s="12" t="s">
+        <v>877</v>
+      </c>
+      <c r="B2452" s="10" t="s">
+        <v>506</v>
+      </c>
+      <c r="C2452" s="10" t="s">
+        <v>571</v>
+      </c>
+      <c r="D2452" s="4" t="s">
+        <v>574</v>
+      </c>
+      <c r="E2452" s="11">
+        <v>3</v>
+      </c>
+      <c r="F2452">
+        <v>70</v>
+      </c>
+      <c r="G2452" t="s">
+        <v>575</v>
+      </c>
+    </row>
+    <row r="2453" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A2453" s="12" t="s">
+        <v>878</v>
+      </c>
+      <c r="B2453" s="10" t="s">
+        <v>507</v>
+      </c>
+      <c r="C2453" s="10" t="s">
+        <v>571</v>
+      </c>
+      <c r="D2453" s="4" t="s">
+        <v>574</v>
+      </c>
+      <c r="E2453" s="11">
+        <v>3</v>
+      </c>
+      <c r="F2453">
+        <v>55</v>
+      </c>
+      <c r="G2453" t="s">
+        <v>579</v>
+      </c>
+    </row>
+    <row r="2454" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A2454" s="12" t="s">
+        <v>879</v>
+      </c>
+      <c r="B2454" s="10" t="s">
+        <v>508</v>
+      </c>
+      <c r="C2454" s="10" t="s">
+        <v>571</v>
+      </c>
+      <c r="D2454" s="4" t="s">
+        <v>574</v>
+      </c>
+      <c r="E2454" s="11">
+        <v>3</v>
+      </c>
+      <c r="F2454">
+        <v>55</v>
+      </c>
+      <c r="G2454" t="s">
+        <v>579</v>
+      </c>
+    </row>
+    <row r="2455" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A2455" s="12" t="s">
+        <v>880</v>
+      </c>
+      <c r="B2455" s="10" t="s">
+        <v>509</v>
+      </c>
+      <c r="C2455" s="10" t="s">
+        <v>571</v>
+      </c>
+      <c r="D2455" s="4" t="s">
+        <v>574</v>
+      </c>
+      <c r="E2455" s="11">
+        <v>3</v>
+      </c>
+      <c r="F2455">
+        <v>55</v>
+      </c>
+      <c r="G2455" t="s">
+        <v>579</v>
+      </c>
+    </row>
+    <row r="2456" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A2456" s="12" t="s">
+        <v>881</v>
+      </c>
+      <c r="B2456" s="10" t="s">
+        <v>491</v>
+      </c>
+      <c r="C2456" s="10" t="s">
+        <v>571</v>
+      </c>
+      <c r="D2456" s="4" t="s">
+        <v>574</v>
+      </c>
+      <c r="E2456" s="11">
+        <v>3</v>
+      </c>
+      <c r="F2456">
+        <v>70</v>
+      </c>
+      <c r="G2456" t="s">
+        <v>575</v>
+      </c>
+    </row>
+    <row r="2457" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A2457" s="12" t="s">
+        <v>882</v>
+      </c>
+      <c r="B2457" s="10" t="s">
+        <v>492</v>
+      </c>
+      <c r="C2457" s="10" t="s">
+        <v>571</v>
+      </c>
+      <c r="D2457" s="4" t="s">
+        <v>574</v>
+      </c>
+      <c r="E2457" s="11">
+        <v>3</v>
+      </c>
+      <c r="F2457">
+        <v>70</v>
+      </c>
+      <c r="G2457" t="s">
+        <v>575</v>
+      </c>
+    </row>
+    <row r="2458" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A2458" s="12" t="s">
+        <v>883</v>
+      </c>
+      <c r="B2458" s="10" t="s">
+        <v>470</v>
+      </c>
+      <c r="C2458" s="10" t="s">
+        <v>571</v>
+      </c>
+      <c r="D2458" s="4" t="s">
+        <v>574</v>
+      </c>
+      <c r="E2458" s="11">
+        <v>3</v>
+      </c>
+      <c r="F2458">
+        <v>70</v>
+      </c>
+      <c r="G2458" t="s">
+        <v>575</v>
+      </c>
+    </row>
+    <row r="2459" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A2459" s="12" t="s">
+        <v>884</v>
+      </c>
+      <c r="B2459" s="10" t="s">
+        <v>471</v>
+      </c>
+      <c r="C2459" s="10" t="s">
+        <v>571</v>
+      </c>
+      <c r="D2459" s="4" t="s">
+        <v>574</v>
+      </c>
+      <c r="E2459" s="11">
+        <v>3</v>
+      </c>
+      <c r="F2459">
+        <v>72</v>
+      </c>
+      <c r="G2459" t="s">
+        <v>575</v>
+      </c>
+    </row>
+    <row r="2460" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A2460" s="12" t="s">
+        <v>885</v>
+      </c>
+      <c r="B2460" s="10" t="s">
+        <v>472</v>
+      </c>
+      <c r="C2460" s="10" t="s">
+        <v>571</v>
+      </c>
+      <c r="D2460" s="4" t="s">
+        <v>574</v>
+      </c>
+      <c r="E2460" s="11">
+        <v>3</v>
+      </c>
+      <c r="F2460">
+        <v>82</v>
+      </c>
+      <c r="G2460" t="s">
+        <v>577</v>
+      </c>
+    </row>
+    <row r="2461" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A2461" s="12" t="s">
+        <v>886</v>
+      </c>
+      <c r="B2461" s="10" t="s">
+        <v>473</v>
+      </c>
+      <c r="C2461" s="10" t="s">
+        <v>571</v>
+      </c>
+      <c r="D2461" s="4" t="s">
+        <v>574</v>
+      </c>
+      <c r="E2461" s="11">
+        <v>3</v>
+      </c>
+      <c r="F2461">
+        <v>67</v>
+      </c>
+      <c r="G2461" t="s">
+        <v>575</v>
+      </c>
+    </row>
+    <row r="2462" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A2462" s="12" t="s">
+        <v>887</v>
+      </c>
+      <c r="B2462" s="10" t="s">
+        <v>474</v>
+      </c>
+      <c r="C2462" s="10" t="s">
+        <v>571</v>
+      </c>
+      <c r="D2462" s="4" t="s">
+        <v>574</v>
+      </c>
+      <c r="E2462" s="11">
+        <v>3</v>
+      </c>
+      <c r="F2462">
+        <v>70</v>
+      </c>
+      <c r="G2462" t="s">
+        <v>575</v>
+      </c>
+    </row>
+    <row r="2463" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A2463" s="12" t="s">
+        <v>888</v>
+      </c>
+      <c r="B2463" s="10" t="s">
+        <v>475</v>
+      </c>
+      <c r="C2463" s="10" t="s">
+        <v>571</v>
+      </c>
+      <c r="D2463" s="4" t="s">
+        <v>574</v>
+      </c>
+      <c r="E2463" s="11">
+        <v>3</v>
+      </c>
+      <c r="F2463">
+        <v>70</v>
+      </c>
+      <c r="G2463" t="s">
+        <v>575</v>
+      </c>
+    </row>
+    <row r="2464" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A2464" s="12" t="s">
+        <v>889</v>
+      </c>
+      <c r="B2464" s="10" t="s">
+        <v>476</v>
+      </c>
+      <c r="C2464" s="10" t="s">
+        <v>571</v>
+      </c>
+      <c r="D2464" s="4" t="s">
+        <v>574</v>
+      </c>
+      <c r="E2464" s="11">
+        <v>3</v>
+      </c>
+      <c r="F2464">
+        <v>88</v>
+      </c>
+      <c r="G2464" t="s">
+        <v>577</v>
+      </c>
+    </row>
+    <row r="2465" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A2465" s="13" t="s">
+        <v>890</v>
+      </c>
+      <c r="B2465" s="10" t="s">
+        <v>477</v>
+      </c>
+      <c r="C2465" s="10" t="s">
+        <v>571</v>
+      </c>
+      <c r="D2465" s="4" t="s">
+        <v>574</v>
+      </c>
+      <c r="E2465" s="11">
+        <v>3</v>
+      </c>
+      <c r="F2465">
+        <v>87</v>
+      </c>
+      <c r="G2465" t="s">
+        <v>577</v>
+      </c>
+    </row>
+    <row r="2466" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A2466" s="13" t="s">
+        <v>891</v>
+      </c>
+      <c r="B2466" s="10" t="s">
+        <v>478</v>
+      </c>
+      <c r="C2466" s="10" t="s">
+        <v>571</v>
+      </c>
+      <c r="D2466" s="4" t="s">
+        <v>574</v>
+      </c>
+      <c r="E2466" s="11">
+        <v>3</v>
+      </c>
+      <c r="F2466">
+        <v>86</v>
+      </c>
+      <c r="G2466" t="s">
+        <v>577</v>
+      </c>
+    </row>
+    <row r="2467" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A2467" s="13" t="s">
+        <v>892</v>
+      </c>
+      <c r="B2467" s="10" t="s">
+        <v>479</v>
+      </c>
+      <c r="C2467" s="10" t="s">
+        <v>571</v>
+      </c>
+      <c r="D2467" s="4" t="s">
+        <v>574</v>
+      </c>
+      <c r="E2467" s="11">
+        <v>3</v>
+      </c>
+      <c r="F2467">
+        <v>69</v>
+      </c>
+      <c r="G2467" t="s">
+        <v>575</v>
+      </c>
+    </row>
+    <row r="2468" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A2468" s="13" t="s">
+        <v>893</v>
+      </c>
+      <c r="B2468" s="10" t="s">
+        <v>469</v>
+      </c>
+      <c r="C2468" s="10" t="s">
+        <v>571</v>
+      </c>
+      <c r="D2468" s="4" t="s">
+        <v>574</v>
+      </c>
+      <c r="E2468" s="11">
+        <v>3</v>
+      </c>
+      <c r="F2468">
+        <v>70</v>
+      </c>
+      <c r="G2468" t="s">
+        <v>575</v>
+      </c>
+    </row>
+    <row r="2469" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A2469" s="13" t="s">
+        <v>894</v>
+      </c>
+      <c r="B2469" s="10" t="s">
+        <v>481</v>
+      </c>
+      <c r="C2469" s="10" t="s">
+        <v>571</v>
+      </c>
+      <c r="D2469" s="4" t="s">
+        <v>574</v>
+      </c>
+      <c r="E2469" s="11">
+        <v>3</v>
+      </c>
+      <c r="F2469">
+        <v>100</v>
+      </c>
+      <c r="G2469" t="s">
+        <v>593</v>
+      </c>
+    </row>
+    <row r="2470" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A2470" s="13" t="s">
+        <v>895</v>
+      </c>
+      <c r="B2470" s="10" t="s">
+        <v>569</v>
+      </c>
+      <c r="C2470" s="10" t="s">
+        <v>571</v>
+      </c>
+      <c r="D2470" s="4" t="s">
+        <v>574</v>
+      </c>
+      <c r="E2470" s="11">
+        <v>3</v>
+      </c>
+      <c r="F2470">
+        <v>67</v>
+      </c>
+      <c r="G2470" t="s">
+        <v>575</v>
+      </c>
+    </row>
+    <row r="2471" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A2471" s="13" t="s">
+        <v>896</v>
+      </c>
+      <c r="B2471" s="10" t="s">
+        <v>484</v>
+      </c>
+      <c r="C2471" s="10" t="s">
+        <v>571</v>
+      </c>
+      <c r="D2471" s="4" t="s">
+        <v>574</v>
+      </c>
+      <c r="E2471" s="11">
+        <v>3</v>
+      </c>
+      <c r="F2471">
+        <v>70</v>
+      </c>
+      <c r="G2471" t="s">
+        <v>575</v>
+      </c>
+    </row>
+    <row r="2472" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A2472" s="13" t="s">
+        <v>897</v>
+      </c>
+      <c r="B2472" s="10" t="s">
+        <v>486</v>
+      </c>
+      <c r="C2472" s="10" t="s">
+        <v>571</v>
+      </c>
+      <c r="D2472" s="4" t="s">
+        <v>574</v>
+      </c>
+      <c r="E2472" s="11">
+        <v>3</v>
+      </c>
+      <c r="F2472">
+        <v>55</v>
+      </c>
+      <c r="G2472" t="s">
+        <v>579</v>
+      </c>
+    </row>
+    <row r="2473" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A2473" s="13" t="s">
+        <v>898</v>
+      </c>
+      <c r="B2473" s="10" t="s">
+        <v>487</v>
+      </c>
+      <c r="C2473" s="10" t="s">
+        <v>571</v>
+      </c>
+      <c r="D2473" s="4" t="s">
+        <v>574</v>
+      </c>
+      <c r="E2473" s="11">
+        <v>3</v>
+      </c>
+      <c r="F2473">
+        <v>80</v>
+      </c>
+      <c r="G2473" t="s">
+        <v>577</v>
+      </c>
+    </row>
+    <row r="2474" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A2474" s="13" t="s">
+        <v>899</v>
+      </c>
+      <c r="B2474" s="10" t="s">
+        <v>488</v>
+      </c>
+      <c r="C2474" s="10" t="s">
+        <v>571</v>
+      </c>
+      <c r="D2474" s="4" t="s">
+        <v>574</v>
+      </c>
+      <c r="E2474" s="11">
+        <v>3</v>
+      </c>
+      <c r="F2474">
+        <v>82</v>
+      </c>
+      <c r="G2474" t="s">
+        <v>577</v>
+      </c>
+    </row>
+    <row r="2475" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A2475" s="13" t="s">
+        <v>900</v>
+      </c>
+      <c r="B2475" s="10" t="s">
+        <v>489</v>
+      </c>
+      <c r="C2475" s="10" t="s">
+        <v>571</v>
+      </c>
+      <c r="D2475" s="4" t="s">
+        <v>574</v>
+      </c>
+      <c r="E2475" s="11">
+        <v>3</v>
+      </c>
+      <c r="F2475">
+        <v>72</v>
+      </c>
+      <c r="G2475" t="s">
+        <v>575</v>
+      </c>
+    </row>
+    <row r="2476" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A2476" s="13" t="s">
+        <v>901</v>
+      </c>
+      <c r="B2476" s="10" t="s">
+        <v>490</v>
+      </c>
+      <c r="C2476" s="10" t="s">
+        <v>571</v>
+      </c>
+      <c r="D2476" s="4" t="s">
+        <v>574</v>
+      </c>
+      <c r="E2476" s="11">
+        <v>3</v>
+      </c>
+      <c r="F2476">
+        <v>67</v>
+      </c>
+      <c r="G2476" t="s">
+        <v>575</v>
+      </c>
+    </row>
+    <row r="2477" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A2477" s="13" t="s">
+        <v>902</v>
+      </c>
+      <c r="B2477" s="10" t="s">
+        <v>533</v>
+      </c>
+      <c r="C2477" s="10" t="s">
+        <v>572</v>
+      </c>
+      <c r="D2477" s="4" t="s">
+        <v>574</v>
+      </c>
+      <c r="E2477" s="11">
+        <v>3</v>
+      </c>
+      <c r="F2477">
+        <v>70</v>
+      </c>
+      <c r="G2477" t="s">
+        <v>575</v>
+      </c>
+    </row>
+    <row r="2478" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A2478" s="13" t="s">
+        <v>903</v>
+      </c>
+      <c r="B2478" s="10" t="s">
+        <v>535</v>
+      </c>
+      <c r="C2478" s="10" t="s">
+        <v>572</v>
+      </c>
+      <c r="D2478" s="4" t="s">
+        <v>574</v>
+      </c>
+      <c r="E2478" s="11">
+        <v>3</v>
+      </c>
+      <c r="F2478">
+        <v>70</v>
+      </c>
+      <c r="G2478" t="s">
+        <v>575</v>
+      </c>
+    </row>
+    <row r="2479" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A2479" s="13" t="s">
+        <v>904</v>
+      </c>
+      <c r="B2479" s="10" t="s">
+        <v>536</v>
+      </c>
+      <c r="C2479" s="10" t="s">
+        <v>572</v>
+      </c>
+      <c r="D2479" s="4" t="s">
+        <v>574</v>
+      </c>
+      <c r="E2479" s="11">
+        <v>3</v>
+      </c>
+      <c r="F2479">
+        <v>100</v>
+      </c>
+      <c r="G2479" t="s">
+        <v>593</v>
+      </c>
+    </row>
+    <row r="2480" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A2480" s="13" t="s">
+        <v>905</v>
+      </c>
+      <c r="B2480" s="10" t="s">
+        <v>537</v>
+      </c>
+      <c r="C2480" s="10" t="s">
+        <v>572</v>
+      </c>
+      <c r="D2480" s="4" t="s">
+        <v>574</v>
+      </c>
+      <c r="E2480" s="11">
+        <v>3</v>
+      </c>
+      <c r="F2480">
+        <v>71</v>
+      </c>
+      <c r="G2480" t="s">
+        <v>575</v>
+      </c>
+    </row>
+    <row r="2481" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A2481" s="13" t="s">
+        <v>906</v>
+      </c>
+      <c r="B2481" s="10" t="s">
+        <v>539</v>
+      </c>
+      <c r="C2481" s="10" t="s">
+        <v>572</v>
+      </c>
+      <c r="D2481" s="4" t="s">
+        <v>574</v>
+      </c>
+      <c r="E2481" s="11">
+        <v>3</v>
+      </c>
+      <c r="F2481">
+        <v>70</v>
+      </c>
+      <c r="G2481" t="s">
+        <v>575</v>
+      </c>
+    </row>
+    <row r="2482" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A2482" s="13" t="s">
+        <v>907</v>
+      </c>
+      <c r="B2482" s="10" t="s">
+        <v>540</v>
+      </c>
+      <c r="C2482" s="10" t="s">
+        <v>572</v>
+      </c>
+      <c r="D2482" s="4" t="s">
+        <v>574</v>
+      </c>
+      <c r="E2482" s="11">
+        <v>3</v>
+      </c>
+      <c r="F2482">
+        <v>71</v>
+      </c>
+      <c r="G2482" t="s">
+        <v>575</v>
+      </c>
+    </row>
+    <row r="2483" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A2483" s="13" t="s">
+        <v>908</v>
+      </c>
+      <c r="B2483" s="10" t="s">
+        <v>541</v>
+      </c>
+      <c r="C2483" s="10" t="s">
+        <v>572</v>
+      </c>
+      <c r="D2483" s="4" t="s">
+        <v>574</v>
+      </c>
+      <c r="E2483" s="11">
+        <v>3</v>
+      </c>
+      <c r="F2483">
+        <v>100</v>
+      </c>
+      <c r="G2483" t="s">
+        <v>593</v>
+      </c>
+    </row>
+    <row r="2484" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A2484" s="13" t="s">
+        <v>909</v>
+      </c>
+      <c r="B2484" s="10" t="s">
+        <v>542</v>
+      </c>
+      <c r="C2484" s="10" t="s">
+        <v>572</v>
+      </c>
+      <c r="D2484" s="4" t="s">
+        <v>574</v>
+      </c>
+      <c r="E2484" s="11">
+        <v>3</v>
+      </c>
+      <c r="F2484">
+        <v>70</v>
+      </c>
+      <c r="G2484" t="s">
+        <v>575</v>
+      </c>
+    </row>
+    <row r="2485" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A2485" s="13" t="s">
+        <v>910</v>
+      </c>
+      <c r="B2485" s="10" t="s">
+        <v>550</v>
+      </c>
+      <c r="C2485" s="10" t="s">
+        <v>572</v>
+      </c>
+      <c r="D2485" s="4" t="s">
+        <v>574</v>
+      </c>
+      <c r="E2485" s="11">
+        <v>3</v>
+      </c>
+      <c r="F2485">
+        <v>78</v>
+      </c>
+      <c r="G2485" t="s">
+        <v>575</v>
+      </c>
+    </row>
+    <row r="2486" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A2486" s="13" t="s">
+        <v>911</v>
+      </c>
+      <c r="B2486" s="10" t="s">
+        <v>532</v>
+      </c>
+      <c r="C2486" s="10" t="s">
+        <v>572</v>
+      </c>
+      <c r="D2486" s="4" t="s">
+        <v>574</v>
+      </c>
+      <c r="E2486" s="11">
+        <v>3</v>
+      </c>
+      <c r="F2486">
+        <v>95</v>
+      </c>
+      <c r="G2486" t="s">
+        <v>593</v>
+      </c>
+    </row>
+    <row r="2487" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A2487" s="13" t="s">
+        <v>912</v>
+      </c>
+      <c r="B2487" s="10" t="s">
+        <v>545</v>
+      </c>
+      <c r="C2487" s="10" t="s">
+        <v>572</v>
+      </c>
+      <c r="D2487" s="4" t="s">
+        <v>574</v>
+      </c>
+      <c r="E2487" s="11">
+        <v>3</v>
+      </c>
+      <c r="F2487">
+        <v>77</v>
+      </c>
+      <c r="G2487" t="s">
+        <v>575</v>
+      </c>
+    </row>
+    <row r="2488" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A2488" s="13" t="s">
+        <v>913</v>
+      </c>
+      <c r="B2488" s="10" t="s">
+        <v>546</v>
+      </c>
+      <c r="C2488" s="10" t="s">
+        <v>572</v>
+      </c>
+      <c r="D2488" s="4" t="s">
+        <v>574</v>
+      </c>
+      <c r="E2488" s="11">
+        <v>3</v>
+      </c>
+      <c r="F2488">
+        <v>55</v>
+      </c>
+      <c r="G2488" t="s">
+        <v>579</v>
+      </c>
+    </row>
+    <row r="2489" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A2489" s="13" t="s">
+        <v>914</v>
+      </c>
+      <c r="B2489" s="10" t="s">
+        <v>547</v>
+      </c>
+      <c r="C2489" s="10" t="s">
+        <v>572</v>
+      </c>
+      <c r="D2489" s="4" t="s">
+        <v>574</v>
+      </c>
+      <c r="E2489" s="11">
+        <v>3</v>
+      </c>
+      <c r="F2489">
+        <v>70</v>
+      </c>
+      <c r="G2489" t="s">
+        <v>575</v>
+      </c>
+    </row>
+    <row r="2490" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A2490" s="13" t="s">
+        <v>915</v>
+      </c>
+      <c r="B2490" s="10" t="s">
+        <v>543</v>
+      </c>
+      <c r="C2490" s="10" t="s">
+        <v>572</v>
+      </c>
+      <c r="D2490" s="4" t="s">
+        <v>574</v>
+      </c>
+      <c r="E2490" s="11">
+        <v>3</v>
+      </c>
+      <c r="F2490">
+        <v>70</v>
+      </c>
+      <c r="G2490" t="s">
+        <v>575</v>
+      </c>
+    </row>
+    <row r="2491" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A2491" s="13" t="s">
+        <v>916</v>
+      </c>
+      <c r="B2491" s="10" t="s">
+        <v>521</v>
+      </c>
+      <c r="C2491" s="10" t="s">
+        <v>572</v>
+      </c>
+      <c r="D2491" s="4" t="s">
+        <v>574</v>
+      </c>
+      <c r="E2491" s="11">
+        <v>3</v>
+      </c>
+      <c r="F2491">
+        <v>72</v>
+      </c>
+      <c r="G2491" t="s">
+        <v>575</v>
+      </c>
+    </row>
+    <row r="2492" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A2492" s="13" t="s">
+        <v>917</v>
+      </c>
+      <c r="B2492" s="10" t="s">
+        <v>520</v>
+      </c>
+      <c r="C2492" s="10" t="s">
+        <v>572</v>
+      </c>
+      <c r="D2492" s="4" t="s">
+        <v>574</v>
+      </c>
+      <c r="E2492" s="11">
+        <v>3</v>
+      </c>
+      <c r="F2492">
+        <v>71</v>
+      </c>
+      <c r="G2492" t="s">
+        <v>575</v>
+      </c>
+    </row>
+    <row r="2493" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A2493" s="13" t="s">
+        <v>918</v>
+      </c>
+      <c r="B2493" s="10" t="s">
+        <v>519</v>
+      </c>
+      <c r="C2493" s="10" t="s">
+        <v>572</v>
+      </c>
+      <c r="D2493" s="4" t="s">
+        <v>574</v>
+      </c>
+      <c r="E2493" s="11">
+        <v>3</v>
+      </c>
+      <c r="F2493">
+        <v>82</v>
+      </c>
+      <c r="G2493" t="s">
+        <v>577</v>
+      </c>
+    </row>
+    <row r="2494" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A2494" s="13" t="s">
+        <v>919</v>
+      </c>
+      <c r="B2494" s="10" t="s">
+        <v>518</v>
+      </c>
+      <c r="C2494" s="10" t="s">
+        <v>572</v>
+      </c>
+      <c r="D2494" s="4" t="s">
+        <v>574</v>
+      </c>
+      <c r="E2494" s="11">
+        <v>3</v>
+      </c>
+      <c r="F2494">
+        <v>86</v>
+      </c>
+      <c r="G2494" t="s">
+        <v>577</v>
+      </c>
+    </row>
+    <row r="2495" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A2495" s="13" t="s">
+        <v>920</v>
+      </c>
+      <c r="B2495" s="10" t="s">
+        <v>516</v>
+      </c>
+      <c r="C2495" s="10" t="s">
+        <v>572</v>
+      </c>
+      <c r="D2495" s="4" t="s">
+        <v>574</v>
+      </c>
+      <c r="E2495" s="11">
+        <v>3</v>
+      </c>
+      <c r="F2495">
+        <v>91</v>
+      </c>
+      <c r="G2495" t="s">
+        <v>593</v>
+      </c>
+    </row>
+    <row r="2496" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A2496" s="13" t="s">
+        <v>921</v>
+      </c>
+      <c r="B2496" s="10" t="s">
+        <v>515</v>
+      </c>
+      <c r="C2496" s="10" t="s">
+        <v>572</v>
+      </c>
+      <c r="D2496" s="4" t="s">
+        <v>574</v>
+      </c>
+      <c r="E2496" s="11">
+        <v>3</v>
+      </c>
+      <c r="F2496">
+        <v>55</v>
+      </c>
+      <c r="G2496" t="s">
+        <v>579</v>
+      </c>
+    </row>
+    <row r="2497" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A2497" s="13" t="s">
+        <v>922</v>
+      </c>
+      <c r="B2497" s="10" t="s">
+        <v>512</v>
+      </c>
+      <c r="C2497" s="10" t="s">
+        <v>572</v>
+      </c>
+      <c r="D2497" s="4" t="s">
+        <v>574</v>
+      </c>
+      <c r="E2497" s="11">
+        <v>3</v>
+      </c>
+      <c r="F2497">
+        <v>73</v>
+      </c>
+      <c r="G2497" t="s">
+        <v>575</v>
+      </c>
+    </row>
+    <row r="2498" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A2498" s="13" t="s">
+        <v>923</v>
+      </c>
+      <c r="B2498" s="10" t="s">
+        <v>511</v>
+      </c>
+      <c r="C2498" s="10" t="s">
+        <v>572</v>
+      </c>
+      <c r="D2498" s="4" t="s">
+        <v>574</v>
+      </c>
+      <c r="E2498" s="11">
+        <v>3</v>
+      </c>
+      <c r="F2498">
+        <v>73</v>
+      </c>
+      <c r="G2498" t="s">
+        <v>575</v>
+      </c>
+    </row>
+    <row r="2499" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A2499" s="13" t="s">
+        <v>924</v>
+      </c>
+      <c r="B2499" s="10" t="s">
+        <v>522</v>
+      </c>
+      <c r="C2499" s="10" t="s">
+        <v>572</v>
+      </c>
+      <c r="D2499" s="4" t="s">
+        <v>574</v>
+      </c>
+      <c r="E2499" s="11">
+        <v>3</v>
+      </c>
+      <c r="F2499">
+        <v>77</v>
+      </c>
+      <c r="G2499" t="s">
+        <v>575</v>
+      </c>
+    </row>
+    <row r="2500" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A2500" s="13" t="s">
+        <v>925</v>
+      </c>
+      <c r="B2500" s="10" t="s">
+        <v>524</v>
+      </c>
+      <c r="C2500" s="10" t="s">
+        <v>572</v>
+      </c>
+      <c r="D2500" s="4" t="s">
+        <v>574</v>
+      </c>
+      <c r="E2500" s="11">
+        <v>3</v>
+      </c>
+      <c r="F2500">
+        <v>100</v>
+      </c>
+      <c r="G2500" t="s">
+        <v>593</v>
+      </c>
+    </row>
+    <row r="2501" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A2501" s="13" t="s">
+        <v>926</v>
+      </c>
+      <c r="B2501" s="10" t="s">
+        <v>525</v>
+      </c>
+      <c r="C2501" s="10" t="s">
+        <v>572</v>
+      </c>
+      <c r="D2501" s="4" t="s">
+        <v>574</v>
+      </c>
+      <c r="E2501" s="11">
+        <v>3</v>
+      </c>
+      <c r="F2501">
+        <v>91</v>
+      </c>
+      <c r="G2501" t="s">
+        <v>593</v>
+      </c>
+    </row>
+    <row r="2502" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A2502" s="13" t="s">
+        <v>927</v>
+      </c>
+      <c r="B2502" s="10" t="s">
+        <v>526</v>
+      </c>
+      <c r="C2502" s="10" t="s">
+        <v>572</v>
+      </c>
+      <c r="D2502" s="4" t="s">
+        <v>574</v>
+      </c>
+      <c r="E2502" s="11">
+        <v>3</v>
+      </c>
+      <c r="F2502">
+        <v>70</v>
+      </c>
+      <c r="G2502" t="s">
+        <v>575</v>
+      </c>
+    </row>
+    <row r="2503" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A2503" s="13" t="s">
+        <v>928</v>
+      </c>
+      <c r="B2503" s="10" t="s">
+        <v>527</v>
+      </c>
+      <c r="C2503" s="10" t="s">
+        <v>572</v>
+      </c>
+      <c r="D2503" s="4" t="s">
+        <v>574</v>
+      </c>
+      <c r="E2503" s="11">
+        <v>3</v>
+      </c>
+      <c r="F2503">
+        <v>73</v>
+      </c>
+      <c r="G2503" t="s">
+        <v>575</v>
+      </c>
+    </row>
+    <row r="2504" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A2504" s="13" t="s">
+        <v>929</v>
+      </c>
+      <c r="B2504" s="10" t="s">
+        <v>528</v>
+      </c>
+      <c r="C2504" s="10" t="s">
+        <v>572</v>
+      </c>
+      <c r="D2504" s="4" t="s">
+        <v>574</v>
+      </c>
+      <c r="E2504" s="11">
+        <v>3</v>
+      </c>
+      <c r="F2504">
+        <v>73</v>
+      </c>
+      <c r="G2504" t="s">
+        <v>575</v>
+      </c>
+    </row>
+    <row r="2505" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A2505" s="13" t="s">
+        <v>930</v>
+      </c>
+      <c r="B2505" s="10" t="s">
+        <v>529</v>
+      </c>
+      <c r="C2505" s="10" t="s">
+        <v>572</v>
+      </c>
+      <c r="D2505" s="4" t="s">
+        <v>574</v>
+      </c>
+      <c r="E2505" s="11">
+        <v>3</v>
+      </c>
+      <c r="F2505">
+        <v>73</v>
+      </c>
+      <c r="G2505" t="s">
+        <v>575</v>
+      </c>
+    </row>
   </sheetData>
+  <phoneticPr fontId="4" type="noConversion"/>
+  <conditionalFormatting sqref="A2200:A2505">
+    <cfRule type="duplicateValues" dxfId="8" priority="1"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A2200:A2505">
+    <cfRule type="duplicateValues" dxfId="7" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="6" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="5" priority="8"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A2397:A2407">
+    <cfRule type="duplicateValues" dxfId="4" priority="6"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A2408:A2419">
+    <cfRule type="duplicateValues" dxfId="3" priority="5"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A2420:A2450">
+    <cfRule type="duplicateValues" dxfId="2" priority="7"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A2451:A2466">
+    <cfRule type="duplicateValues" dxfId="1" priority="4"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A2200:A2505">
+    <cfRule type="duplicateValues" dxfId="0" priority="9"/>
+  </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>